--- a/AAII_Financials/Quarterly/DCI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DCI_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="92">
   <si>
     <t>DCI</t>
   </si>
@@ -656,416 +656,442 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45230</v>
+      </c>
+      <c r="F7" s="2">
         <v>45138</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45046</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>44957</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44865</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44773</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44681</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44592</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44500</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44408</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44316</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44227</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44135</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44043</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43951</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43861</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43769</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43677</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43585</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43496</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43404</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43312</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43220</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43131</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43039</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>42947</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42855</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>42766</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42674</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42582</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>876700</v>
+      </c>
+      <c r="E8" s="3">
+        <v>846300</v>
+      </c>
+      <c r="F8" s="3">
         <v>879500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>875700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>828300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>847300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>890000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>853200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>802500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>760900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>773100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>765000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>679100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>636600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>617400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>629700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>662000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>672700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>727000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>712800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>703700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>701400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>724700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>700000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>664700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>644800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>660100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>608200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>550600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>553000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>593800</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>568100</v>
+      </c>
+      <c r="E9" s="3">
+        <v>545400</v>
+      </c>
+      <c r="F9" s="3">
         <v>579400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>586900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>543900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>560100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>598400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>584200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>552700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>501400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>507400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>507000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>448000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>413900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>409500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>420500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>438800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>441400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>483200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>472100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>478300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>463000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>471700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>460400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>445800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>420500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>430600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>396700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>362700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>358800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>384500</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>308600</v>
+      </c>
+      <c r="E10" s="3">
+        <v>300900</v>
+      </c>
+      <c r="F10" s="3">
         <v>300100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>288800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>284400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>287200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>291600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>269000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>249800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>259500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>265700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>258000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>231100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>222700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>207900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>209200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>223200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>231300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>243800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>240700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>225400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>238400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>253000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>239600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>218900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>224300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>229500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>211500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>187900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>194200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>209300</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1098,28 +1124,30 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>22100</v>
+      </c>
+      <c r="E12" s="3">
+        <v>21300</v>
+      </c>
+      <c r="F12" s="3">
         <v>21900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>19000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>18500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>18700</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>8</v>
@@ -1190,8 +1218,14 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,8 +1316,14 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1308,23 +1348,23 @@
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="3">
         <v>2500</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N14" s="3">
-        <v>14800</v>
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>8</v>
+      <c r="P14" s="3">
+        <v>14800</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>8</v>
@@ -1335,11 +1375,11 @@
       <c r="S14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
@@ -1374,31 +1414,37 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>3800</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
-      </c>
-      <c r="F15" s="3">
-        <v>0</v>
-      </c>
-      <c r="G15" s="3">
-        <v>0</v>
-      </c>
-      <c r="H15" s="3">
-        <v>0</v>
-      </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3">
-        <v>0</v>
+        <v>4000</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1466,8 +1512,14 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1549,206 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>747000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>721700</v>
+      </c>
+      <c r="F17" s="3">
         <v>758900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>751700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>712000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>728000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>760700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>742200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>706800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>653400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>661100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>655600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>603000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>549400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>534900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>545200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>577500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>584000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>622600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>612800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>618600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>602700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>620900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>599100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>583100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>554100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>565800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>519700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>481200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>476600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>503700</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>129700</v>
+      </c>
+      <c r="E18" s="3">
+        <v>124600</v>
+      </c>
+      <c r="F18" s="3">
         <v>120600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>124000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>116300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>119300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>129300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>111000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>95700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>107500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>112000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>109400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>76100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>87200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>82500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>84500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>84500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>88700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>104400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>100000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>85100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>98700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>103800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>100900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>81600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>90700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>94300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>88500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>69400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>76400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>90100</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,468 +1781,500 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>1600</v>
+        <v>4900</v>
       </c>
       <c r="E20" s="3">
-        <v>2600</v>
+        <v>3800</v>
       </c>
       <c r="F20" s="3">
         <v>1600</v>
       </c>
       <c r="G20" s="3">
+        <v>2600</v>
+      </c>
+      <c r="H20" s="3">
+        <v>1600</v>
+      </c>
+      <c r="I20" s="3">
         <v>1800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>3400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>4100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>2400</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>5100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>4700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>1100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-1500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>2700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>4300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>2800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>2600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>4700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>1900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>5300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>3500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>-800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>2500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>1700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>8100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>-2700</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>159200</v>
+      </c>
+      <c r="E21" s="3">
+        <v>152700</v>
+      </c>
+      <c r="F21" s="3">
         <v>147200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>149100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>140300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>143500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>155500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>138600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>121800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>131300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>142000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>137900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>100500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>109000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>108200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>110600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>108900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>112500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>125300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>125300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>105700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>119900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>128400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>123900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>100500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>108800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>116200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>107600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>89500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>103400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>106400</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E22" s="3">
+        <v>5500</v>
+      </c>
+      <c r="F22" s="3">
         <v>4900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>5100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>4600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>4500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>4100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>3800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>3600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>3400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>3100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>3200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>3300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>3500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>3900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>4400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>4500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>4700</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>5200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>5200</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>5300</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>4200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>5600</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>5400</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>5100</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>5200</v>
       </c>
       <c r="AB22" s="3">
         <v>5100</v>
       </c>
       <c r="AC22" s="3">
-        <v>4800</v>
+        <v>5200</v>
       </c>
       <c r="AD22" s="3">
-        <v>4800</v>
+        <v>5100</v>
       </c>
       <c r="AE22" s="3">
         <v>4800</v>
       </c>
       <c r="AF22" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AG22" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AH22" s="3">
         <v>4900</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>129000</v>
+      </c>
+      <c r="E23" s="3">
+        <v>122900</v>
+      </c>
+      <c r="F23" s="3">
         <v>117300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>121500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>113300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>116600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>128600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>111300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>94500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>104100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>114000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>110900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>73900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>82200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>81300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>84400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>82800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>86600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>98800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>99500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>80500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>96400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>103500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>99000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>76400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>84700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>91700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>84300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>66300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>79700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>82500</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>30300</v>
+      </c>
+      <c r="E24" s="3">
+        <v>30800</v>
+      </c>
+      <c r="F24" s="3">
         <v>25400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>27800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>27300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>29400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>27600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>28300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>22700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>27000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>29700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>26500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>17700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>20300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>17200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>21000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>18400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>21600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>21600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>24300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>20000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>23500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>27100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>28700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>119000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>23800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>23500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>24200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>19800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>21700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>23000</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2365,210 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>98700</v>
+      </c>
+      <c r="E26" s="3">
+        <v>92100</v>
+      </c>
+      <c r="F26" s="3">
         <v>91900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>93700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>86000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>87200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>101000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>83000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>71800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>77100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>84300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>84400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>56200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>61900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>64100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>63400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>64400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>65000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>77200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>75200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>60500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>72900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>76400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>70300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-42600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>60900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>68200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>60100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>46500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>58000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>59500</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>98700</v>
+      </c>
+      <c r="E27" s="3">
+        <v>92100</v>
+      </c>
+      <c r="F27" s="3">
         <v>91900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>93700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>86000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>87200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>101000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>83000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>71800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>77100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>84300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>84400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>56200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>61900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>64100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>63400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>64400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>65000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>77200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>75200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>60500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>72900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>76400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>70300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-42600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>60900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>68200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>60100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>46500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>58000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>59500</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2659,14 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2575,11 +2697,11 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-      <c r="M29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N29" s="3" t="s">
-        <v>8</v>
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3">
+        <v>0</v>
       </c>
       <c r="O29" s="3" t="s">
         <v>8</v>
@@ -2596,32 +2718,32 @@
       <c r="S29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T29" s="3">
+      <c r="T29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V29" s="3">
         <v>-19100</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
-      </c>
-      <c r="V29" s="3">
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
         <v>-400</v>
       </c>
-      <c r="W29" s="3">
+      <c r="Y29" s="3">
         <v>900</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Z29" s="3">
         <v>26000</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="AA29" s="3">
         <v>-400</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AB29" s="3">
         <v>-10300</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
@@ -2635,8 +2757,14 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2855,14 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,192 +2953,210 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-1600</v>
+        <v>-4900</v>
       </c>
       <c r="E32" s="3">
-        <v>-2600</v>
+        <v>-3800</v>
       </c>
       <c r="F32" s="3">
         <v>-1600</v>
       </c>
       <c r="G32" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="H32" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="I32" s="3">
         <v>-1800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-3400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-4100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-2400</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-5100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-4700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-1100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>1500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-4300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-2800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-2600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-4700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-1900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-5300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-3500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-2500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-1700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-8100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>98700</v>
+      </c>
+      <c r="E33" s="3">
+        <v>92100</v>
+      </c>
+      <c r="F33" s="3">
         <v>91900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>93700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>86000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>87200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>101000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>83000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>71800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>77100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>84300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>84400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>56200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>61900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>64100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>63400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>64400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>65000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>58100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>75200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>60100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>73800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>102400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>69900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-52900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>60900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>68200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>60100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>46500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>58000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>59500</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3247,215 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>98700</v>
+      </c>
+      <c r="E35" s="3">
+        <v>92100</v>
+      </c>
+      <c r="F35" s="3">
         <v>91900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>93700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>86000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>87200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>101000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>83000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>71800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>77100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>84300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>84400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>56200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>61900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>64100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>63400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>64400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>65000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>58100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>75200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>60100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>73800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>102400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>69900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-52900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>60900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>68200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>60100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>46500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>58000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>59500</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45230</v>
+      </c>
+      <c r="F38" s="2">
         <v>45138</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45046</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>44957</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44865</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44773</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44681</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44592</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44500</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44408</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44316</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44227</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44135</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44043</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43951</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43861</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43769</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43677</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43585</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43496</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43404</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43312</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43220</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43131</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43039</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>42947</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42855</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>42766</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42674</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42582</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3488,10 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,100 +3524,108 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>193800</v>
+      </c>
+      <c r="E41" s="3">
+        <v>217800</v>
+      </c>
+      <c r="F41" s="3">
         <v>187100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>186000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>179400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>161000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>193300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>168700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>170400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>200800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>222800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>215300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>207300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>270000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>236600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>326500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>211100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>210000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>177800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>203800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>191200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>199900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>204700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>317300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>362200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>349600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>308400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>295900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>296300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>262200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>243200</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3536,420 +3716,450 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>610500</v>
+      </c>
+      <c r="E43" s="3">
+        <v>594400</v>
+      </c>
+      <c r="F43" s="3">
         <v>613000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>641700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>592200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>601100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>634300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>604200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>570900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>563400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>567600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>553800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>504300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>476900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>455300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>460500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>475800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>501500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>529500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>534300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>515300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>542400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>534600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>530600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>509900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>483000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>497700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>459200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>408400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>415000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>452400</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>433400</v>
+      </c>
+      <c r="E44" s="3">
+        <v>429600</v>
+      </c>
+      <c r="F44" s="3">
         <v>418100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>449700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>501300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>490100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>502400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>510700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>480700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>444700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>384500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>360100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>347600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>329500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>322700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>346500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>350100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>361500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>332800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>359500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>365600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>360500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>334100</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>344200</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>344900</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>319600</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>293500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>272800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>260400</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>249200</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>234100</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>79500</v>
+      </c>
+      <c r="E45" s="3">
+        <v>71300</v>
+      </c>
+      <c r="F45" s="3">
         <v>67800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>75200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>76200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>83200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>76500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>83700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>92200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>86900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>69100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>69500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>67100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>67200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>82100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>87000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>84200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>86100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>82500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>76000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>85600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>67600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>52300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>57100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>62900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>52100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>51400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>56100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>60100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>66600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>80000</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1317200</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1313100</v>
+      </c>
+      <c r="F46" s="3">
         <v>1286000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>1352600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>1349100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>1335400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>1406500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>1367300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>1314200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>1295800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>1244000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>1198700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>1126300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>1143600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>1096700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>1220500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>1121200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>1159100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>1122600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>1173600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>1157700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>1170400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>1125700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>1249200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>1279900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>1204300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>1151000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>1084000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>1025200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>993000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>1009700</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>24300</v>
+      </c>
+      <c r="E47" s="3">
+        <v>23500</v>
+      </c>
+      <c r="F47" s="3">
         <v>24400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>24300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>20500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>20400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>22400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>25600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>23700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>23900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>24200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>24200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>23300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>22300</v>
-      </c>
-      <c r="P47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="R47" s="3" t="s">
         <v>8</v>
@@ -3957,11 +4167,11 @@
       <c r="S47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T47" s="3">
-        <v>0</v>
-      </c>
-      <c r="U47" s="3">
-        <v>0</v>
+      <c r="T47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V47" s="3">
         <v>0</v>
@@ -3996,192 +4206,210 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>647000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>642300</v>
+      </c>
+      <c r="F48" s="3">
         <v>652900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>640900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>625800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>590800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>594400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>591100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>601000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>609700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>617800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>626300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>624300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>617100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>705300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>685700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>699100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>685500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>588900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>569800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>552500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>517900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>509300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>511100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>507700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>483800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>484600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>462500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>459700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>466100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>2771000</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>655300</v>
+      </c>
+      <c r="E49" s="3">
+        <v>651000</v>
+      </c>
+      <c r="F49" s="3">
         <v>669200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>519100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>446600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>435300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>445600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>410400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>423700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>379800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>384100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>386500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>387400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>379800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>384100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>369100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>378200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>379100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>374000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>383700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>388000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>386700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>274000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>277100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>280200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>277400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>278700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>268100</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>268800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>270500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>306300</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4500,14 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,100 +4598,112 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>139700</v>
+      </c>
+      <c r="E52" s="3">
+        <v>138700</v>
+      </c>
+      <c r="F52" s="3">
         <v>138000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>138600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>136600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>130100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>131400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>124800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>128700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>129300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>130100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>118900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>109800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>106600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>58500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>63200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>63700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>59600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>57100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>78800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>68100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>69000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>67600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>57600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>63500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>66900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>65400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>65700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>64000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>64500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>39700</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4794,112 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2783500</v>
+      </c>
+      <c r="E54" s="3">
+        <v>2768600</v>
+      </c>
+      <c r="F54" s="3">
         <v>2770500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>2675500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>2578600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>2512000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>2600300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>2519200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>2491300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>2438500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>2400200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>2354600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>2271100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>2269400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>2244600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>2338500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>2262200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>2283300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>2142600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>2205900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>2166300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>2144000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>1976600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>2095000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>2131300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>2032400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>1979700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>1880300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>1817700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>1794100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>1787000</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4932,10 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,560 +4968,598 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>325800</v>
+      </c>
+      <c r="E57" s="3">
+        <v>324900</v>
+      </c>
+      <c r="F57" s="3">
         <v>304900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>311100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>302100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>320700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>338500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>335800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>324500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>310000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>293900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>268100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>228100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>209400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>187700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>202700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>210100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>229100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>237500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>238700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>226700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>230600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>201300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>201500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>200000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>190600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>194000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>179000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>157800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>160700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>143300</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>262100</v>
+      </c>
+      <c r="E58" s="3">
+        <v>284800</v>
+      </c>
+      <c r="F58" s="3">
         <v>159100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>151600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>4000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>3700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>31300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>63900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>41200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>48500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>44500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>22400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>6700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>9500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>58100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>84700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>110900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>52300</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>50600</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>66000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>74000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>43500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>4500</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>18100</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>39200</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>73900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>306900</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>277100</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>245000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>216700</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>305600</v>
+      </c>
+      <c r="E59" s="3">
+        <v>272900</v>
+      </c>
+      <c r="F59" s="3">
         <v>292400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>249300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>274000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>248400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>287400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>239400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>250100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>230700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>264200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>236200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>249000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>203300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>209600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>172000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>203400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>191100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>193100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>157100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>200400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>183000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>224600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>191700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>216900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>185300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>216200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>169000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>180600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>157700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>183800</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>893500</v>
+      </c>
+      <c r="E60" s="3">
+        <v>882600</v>
+      </c>
+      <c r="F60" s="3">
         <v>756400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>712000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>580100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>569300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>629600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>606500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>638500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>581900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>606600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>548800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>499500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>419400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>406800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>432800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>498200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>531100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>482900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>446400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>493100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>487600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>469400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>397700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>435000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>415100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>484100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>654900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>615500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>563400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>543800</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>352000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>366600</v>
+      </c>
+      <c r="F61" s="3">
         <v>496600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>470500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>624800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>600700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>644300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>607200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>553900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>548100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>461000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>454600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>495100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>576300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>617400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>735100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>595800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>596800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>584400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>644400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>632500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>630600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>499600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>687500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>667700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>631700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>537300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>298100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>297800</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>324700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>350200</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>162200</v>
+      </c>
+      <c r="E62" s="3">
+        <v>183300</v>
+      </c>
+      <c r="F62" s="3">
         <v>196800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>194300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>179500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>187200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>193200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>181900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>182100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>192600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>195500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>197800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>202100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>210200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>216600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>215800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>217000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>227700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>172600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>157300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>155000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>158500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>149800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>173400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>201700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>104600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>103800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>125300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>123700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>121300</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>121600</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5650,14 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5748,14 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,100 +5846,112 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1407700</v>
+      </c>
+      <c r="E66" s="3">
+        <v>1432500</v>
+      </c>
+      <c r="F66" s="3">
         <v>1449800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>1376800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>1384400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>1357200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>1467100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>1395600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>1374500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>1322600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>1263100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>1201200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>1196700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>1222600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>1257500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>1399700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>1327400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>1371700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>1255300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>1266200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>1298900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>1294400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>1123600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>1263300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>1309000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>1156100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>1129600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>1082600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>1041200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>1013500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>1019600</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5984,10 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +6078,14 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6176,14 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6274,14 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,100 +6372,112 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2219000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>2180200</v>
+      </c>
+      <c r="F72" s="3">
         <v>2087800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>2056500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>1962800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>1932800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>1849000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>1802600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>1718000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>1700400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>1621200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>1591200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>1507600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>1504900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>1445900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>1432800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>1368600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>1361100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>1303200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>1298300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>1223800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>1213800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>1143400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>1089100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>1016400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>1120200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>1056900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>1035900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>977300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>977500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>921800</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6568,14 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6666,14 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6764,112 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1375800</v>
+      </c>
+      <c r="E76" s="3">
+        <v>1336100</v>
+      </c>
+      <c r="F76" s="3">
         <v>1320700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>1298700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>1194200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>1154800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>1133200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>1123600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>1116800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>1115900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>1137100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>1153400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>1074400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>1046800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>987100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>938800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>934800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>911600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>887300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>939700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>867400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>849600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>853000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>831700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>822300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>876300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>850100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>797700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>776500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>780600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>767400</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6960,215 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45322</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45230</v>
+      </c>
+      <c r="F80" s="2">
         <v>45138</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45046</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>44957</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44865</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44773</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44681</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44592</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44500</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44408</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44316</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44227</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44135</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44043</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43951</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43861</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43769</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43677</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43585</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43496</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43404</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43312</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43220</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43131</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43039</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>42947</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42855</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>42766</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42674</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42582</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>98700</v>
+      </c>
+      <c r="E81" s="3">
+        <v>92100</v>
+      </c>
+      <c r="F81" s="3">
         <v>91900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>93700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>86000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>87200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>101000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>83000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>71800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>77100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>84300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>84400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>56200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>61900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>64100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>63400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>64400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>65000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>58100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>75200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>60100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>73800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>102400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>69900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-52900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>60900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>68200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>60100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>46500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>58000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>59500</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,100 +7201,108 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>24600</v>
+      </c>
+      <c r="E83" s="3">
+        <v>24300</v>
+      </c>
+      <c r="F83" s="3">
         <v>25000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>22500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>22400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>22400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>22800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>23500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>23700</v>
-      </c>
-      <c r="K83" s="3">
-        <v>23800</v>
-      </c>
-      <c r="L83" s="3">
-        <v>24900</v>
       </c>
       <c r="M83" s="3">
         <v>23800</v>
       </c>
       <c r="N83" s="3">
+        <v>24900</v>
+      </c>
+      <c r="O83" s="3">
+        <v>23800</v>
+      </c>
+      <c r="P83" s="3">
         <v>23300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>23300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>23000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>21800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>21600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>21200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>21300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>20600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>19900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>19300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>19300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>19500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>19000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>18900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>19400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>18500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>18400</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>18900</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7393,14 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7491,14 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7589,14 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7687,14 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7785,112 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>87000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>138000</v>
+      </c>
+      <c r="F89" s="3">
         <v>190800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>133200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>102300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>118200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>108900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>64100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>36900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>42900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>96300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>103300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>73400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>128900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>121800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>88400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>90700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>86100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>122600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>80400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>79500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>63300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>104200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>48900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>45900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>63900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>87000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>61300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>69800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>99700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>84200</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,100 +7923,108 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-21300</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-23200</v>
+      </c>
+      <c r="F91" s="3">
         <v>-25700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-35200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-29500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-28100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-28700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-23300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-15200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-18300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-18800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-9800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-11600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-18800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-18200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-26500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-42600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-37100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-38300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-45300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-38900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-28200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-24400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-27300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-25900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-19900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-24700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-32400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-37600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-12400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-13500</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +8115,14 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,100 +8213,112 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-21300</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-23200</v>
+      </c>
+      <c r="F94" s="3">
         <v>-172200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-97500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-29500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-28100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-48200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-23300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-64200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-18300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-18100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-9800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-11600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-18800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-22700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-26500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-42600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-37100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-38000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-45300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-38900</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-124200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-23100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-27300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-25900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-19100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-43600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-16200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-12600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-23300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-11300</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,49 +8351,51 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-30100</v>
+      </c>
+      <c r="E96" s="3">
+        <v>-30200</v>
+      </c>
+      <c r="F96" s="3">
         <v>-30300</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>-27900</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>-28000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>-28200</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>-28300</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>-27200</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>-27200</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>-27400</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>-27700</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>-26400</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>-26500</v>
-      </c>
-      <c r="O96" s="3">
-        <v>-26600</v>
-      </c>
-      <c r="P96" s="3">
-        <v>-26600</v>
       </c>
       <c r="Q96" s="3">
         <v>-26600</v>
@@ -7939,46 +8407,52 @@
         <v>-26600</v>
       </c>
       <c r="T96" s="3">
+        <v>-26600</v>
+      </c>
+      <c r="U96" s="3">
+        <v>-26600</v>
+      </c>
+      <c r="V96" s="3">
         <v>-26800</v>
       </c>
-      <c r="U96" s="3">
+      <c r="W96" s="3">
         <v>-24200</v>
       </c>
-      <c r="V96" s="3">
+      <c r="X96" s="3">
         <v>-24300</v>
       </c>
-      <c r="W96" s="3">
+      <c r="Y96" s="3">
         <v>-24400</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Z96" s="3">
         <v>-24500</v>
-      </c>
-      <c r="Y96" s="3">
-        <v>-23400</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>-23400</v>
       </c>
       <c r="AA96" s="3">
         <v>-23400</v>
       </c>
       <c r="AB96" s="3">
+        <v>-23400</v>
+      </c>
+      <c r="AC96" s="3">
+        <v>-23400</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-22900</v>
-      </c>
-      <c r="AC96" s="3">
-        <v>-23200</v>
-      </c>
-      <c r="AD96" s="3">
-        <v>-23100</v>
       </c>
       <c r="AE96" s="3">
         <v>-23200</v>
       </c>
       <c r="AF96" s="3">
+        <v>-23100</v>
+      </c>
+      <c r="AG96" s="3">
+        <v>-23200</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-23300</v>
       </c>
     </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8543,14 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8641,14 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,280 +8739,304 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-92800</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-78900</v>
+      </c>
+      <c r="F100" s="3">
         <v>-18100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-27300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-64000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-112800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-31400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-37100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-45500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-67800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-84900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-131700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-78900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-195800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>59300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-48300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-14700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-109600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-19700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-55300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>61300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-184700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-61500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-20700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-40000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-46200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-16300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-55200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>-73500</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="F101" s="3">
         <v>600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-1800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>9600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-9600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-4700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-5400</v>
-      </c>
-      <c r="J101" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="K101" s="3">
-        <v>-1100</v>
       </c>
       <c r="L101" s="3">
         <v>-2900</v>
       </c>
       <c r="M101" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="N101" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="O101" s="3">
         <v>-600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>7200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>2200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>6800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-5800</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>1300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-2100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>-1000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>-2800</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>6000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>-5200</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>-9000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>-5000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>13300</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>-1700</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>9900</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>2200</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>-1600</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AG101" s="3">
         <v>-2200</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AH101" s="3">
         <v>-3600</v>
       </c>
     </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-24000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>30700</v>
+      </c>
+      <c r="F102" s="3">
         <v>1100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>6600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>18400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-32300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>24600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-1700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-30400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-22000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>7500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>8000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-62700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>33400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-89900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>115400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>1100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>32200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-26000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>12600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-8700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-4800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-112600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-44900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>12600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>41200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>12500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>-400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>34100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>19000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>-4200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DCI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DCI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="92">
   <si>
     <t>DCI</t>
   </si>
@@ -656,442 +656,454 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45412</v>
+      </c>
+      <c r="E7" s="2">
         <v>45322</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45230</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45138</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45046</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44957</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44865</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44773</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44681</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44592</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44500</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44408</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44316</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44227</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44135</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44043</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43951</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43861</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43769</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43677</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43585</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43496</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43404</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43312</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43220</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43131</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43039</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42947</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42855</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42766</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42674</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42582</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>927900</v>
+      </c>
+      <c r="E8" s="3">
         <v>876700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>846300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>879500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>875700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>828300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>847300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>890000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>853200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>802500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>760900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>773100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>765000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>679100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>636600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>617400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>629700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>662000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>672700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>727000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>712800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>703700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>701400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>724700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>700000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>664700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>644800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>660100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>608200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>550600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>553000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>593800</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>597800</v>
+      </c>
+      <c r="E9" s="3">
         <v>568100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>545400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>579400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>586900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>543900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>560100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>598400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>584200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>552700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>501400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>507400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>507000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>448000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>413900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>409500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>420500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>438800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>441400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>483200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>472100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>478300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>463000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>471700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>460400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>445800</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>420500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>430600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>396700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>362700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>358800</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>384500</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>330100</v>
+      </c>
+      <c r="E10" s="3">
         <v>308600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>300900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>300100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>288800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>284400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>287200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>291600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>269000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>249800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>259500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>265700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>258000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>231100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>222700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>207900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>209200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>223200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>231300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>243800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>240700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>225400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>238400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>253000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>239600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>218900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>224300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>229500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>211500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>187900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>194200</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>209300</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1126,31 +1138,32 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>24800</v>
+      </c>
+      <c r="E12" s="3">
         <v>22100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>21300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>21900</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>19000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>18500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>18700</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>8</v>
@@ -1224,8 +1237,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1322,8 +1338,11 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1354,20 +1373,20 @@
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="3">
         <v>2500</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3" t="s">
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>14800</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>8</v>
@@ -1381,8 +1400,8 @@
       <c r="U14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
@@ -1420,19 +1439,22 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E15" s="3">
         <v>3800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>4000</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>8</v>
@@ -1446,8 +1468,8 @@
       <c r="J15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
+      <c r="K15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -1518,8 +1540,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1551,204 +1576,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>784300</v>
+      </c>
+      <c r="E17" s="3">
         <v>747000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>721700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>758900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>751700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>712000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>728000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>760700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>742200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>706800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>653400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>661100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>655600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>603000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>549400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>534900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>545200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>577500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>584000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>622600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>612800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>618600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>602700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>620900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>599100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>583100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>554100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>565800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>519700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>481200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>476600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>503700</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>143600</v>
+      </c>
+      <c r="E18" s="3">
         <v>129700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>124600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>120600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>124000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>116300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>119300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>129300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>111000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>95700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>107500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>112000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>109400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>76100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>87200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>82500</v>
-      </c>
-      <c r="S18" s="3">
-        <v>84500</v>
       </c>
       <c r="T18" s="3">
         <v>84500</v>
       </c>
       <c r="U18" s="3">
+        <v>84500</v>
+      </c>
+      <c r="V18" s="3">
         <v>88700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>104400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>100000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>85100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>98700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>103800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>100900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>81600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>90700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>94300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>88500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>69400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>76400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>90100</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1783,290 +1815,297 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E20" s="3">
         <v>4900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>3800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>2600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>3400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>4100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2400</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>5100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>4700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>2700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>4300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>2800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>2600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>4700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>1900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>5300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>3500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>2500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>1700</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>8100</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-2700</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>173600</v>
+      </c>
+      <c r="E21" s="3">
         <v>159200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>152700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>147200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>149100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>140300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>143500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>155500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>138600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>121800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>131300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>142000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>137900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>100500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>109000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>108200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>110600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>108900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>112500</v>
-      </c>
-      <c r="V21" s="3">
-        <v>125300</v>
       </c>
       <c r="W21" s="3">
         <v>125300</v>
       </c>
       <c r="X21" s="3">
+        <v>125300</v>
+      </c>
+      <c r="Y21" s="3">
         <v>105700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>119900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>128400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>123900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>100500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>108800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>116200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>107600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>89500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>103400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>106400</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E22" s="3">
         <v>5600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>5500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>4900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>5100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>4600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>4500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>4100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>3800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>3600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>3400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>3100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>3200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>3300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>3500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>3900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>4400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>4500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>4700</v>
-      </c>
-      <c r="V22" s="3">
-        <v>5200</v>
       </c>
       <c r="W22" s="3">
         <v>5200</v>
       </c>
       <c r="X22" s="3">
+        <v>5200</v>
+      </c>
+      <c r="Y22" s="3">
         <v>5300</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>4200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>5600</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>5400</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>5100</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>5200</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>5100</v>
-      </c>
-      <c r="AE22" s="3">
-        <v>4800</v>
       </c>
       <c r="AF22" s="3">
         <v>4800</v>
@@ -2075,206 +2114,215 @@
         <v>4800</v>
       </c>
       <c r="AH22" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AI22" s="3">
         <v>4900</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>144000</v>
+      </c>
+      <c r="E23" s="3">
         <v>129000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>122900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>117300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>121500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>113300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>116600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>128600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>111300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>94500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>104100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>114000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>110900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>73900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>82200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>81300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>84400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>82800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>86600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>98800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>99500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>80500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>96400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>103500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>99000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>76400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>84700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>91700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>84300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>66300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>79700</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>82500</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>30500</v>
+      </c>
+      <c r="E24" s="3">
         <v>30300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>30800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>25400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>27800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>27300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>29400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>27600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>28300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>22700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>27000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>29700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>26500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>17700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>20300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>17200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>21000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>18400</v>
-      </c>
-      <c r="U24" s="3">
-        <v>21600</v>
       </c>
       <c r="V24" s="3">
         <v>21600</v>
       </c>
       <c r="W24" s="3">
+        <v>21600</v>
+      </c>
+      <c r="X24" s="3">
         <v>24300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>20000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>23500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>27100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>28700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>119000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>23800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>23500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>24200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>19800</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>21700</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>23000</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2371,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>113500</v>
+      </c>
+      <c r="E26" s="3">
         <v>98700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>92100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>91900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>93700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>86000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>87200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>101000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>83000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>71800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>77100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>84300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>84400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>56200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>61900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>64100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>63400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>64400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>65000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>77200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>75200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>60500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>72900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>76400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>70300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-42600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>60900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>68200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>60100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>46500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>58000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>59500</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>113500</v>
+      </c>
+      <c r="E27" s="3">
         <v>98700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>92100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>91900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>93700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>86000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>87200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>101000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>83000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>71800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>77100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>84300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>84400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>56200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>61900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>64100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>63400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>64400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>65000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>77200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>75200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>60500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>72900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>76400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>70300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-42600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>60900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>68200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>60100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>46500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>58000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>59500</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2665,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2703,8 +2763,8 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-      <c r="O29" s="3" t="s">
-        <v>8</v>
+      <c r="O29" s="3">
+        <v>0</v>
       </c>
       <c r="P29" s="3" t="s">
         <v>8</v>
@@ -2724,29 +2784,29 @@
       <c r="U29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V29" s="3">
+      <c r="V29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="W29" s="3">
         <v>-19100</v>
       </c>
-      <c r="W29" s="3">
-        <v>0</v>
-      </c>
       <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
         <v>-400</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>900</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>26000</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>-400</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>-10300</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
@@ -2763,8 +2823,11 @@
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2861,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2959,204 +3025,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-4900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-3800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-2600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-3400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-4100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2400</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-5100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-4700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-2700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-4300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-2800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-2600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-4700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-1900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-5300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-3500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-2500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-1700</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-8100</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>113500</v>
+      </c>
+      <c r="E33" s="3">
         <v>98700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>92100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>91900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>93700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>86000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>87200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>101000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>83000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>71800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>77100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>84300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>84400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>56200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>61900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>64100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>63400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>64400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>65000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>58100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>75200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>60100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>73800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>102400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>69900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-52900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>60900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>68200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>60100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>46500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>58000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>59500</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3253,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>113500</v>
+      </c>
+      <c r="E35" s="3">
         <v>98700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>92100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>91900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>93700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>86000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>87200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>101000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>83000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>71800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>77100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>84300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>84400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>56200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>61900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>64100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>63400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>64400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>65000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>58100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>75200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>60100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>73800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>102400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>69900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-52900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>60900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>68200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>60100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>46500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>58000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>59500</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45412</v>
+      </c>
+      <c r="E38" s="2">
         <v>45322</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45230</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45138</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45046</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44957</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44865</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44773</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44681</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44592</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44500</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44408</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44316</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44227</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44135</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44043</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43951</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43861</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43769</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43677</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43585</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43496</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43404</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43312</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43220</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43131</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43039</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42947</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42855</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42766</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42674</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42582</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3490,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3526,106 +3611,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>223700</v>
+      </c>
+      <c r="E41" s="3">
         <v>193800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>217800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>187100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>186000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>179400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>161000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>193300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>168700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>170400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>200800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>222800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>215300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>207300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>270000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>236600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>326500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>211100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>210000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>177800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>203800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>191200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>199900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>204700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>317300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>362200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>349600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>308400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>295900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>296300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>262200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>243200</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3722,447 +3811,462 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>653200</v>
+      </c>
+      <c r="E43" s="3">
         <v>610500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>594400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>613000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>641700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>592200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>601100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>634300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>604200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>570900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>563400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>567600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>553800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>504300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>476900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>455300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>460500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>475800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>501500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>529500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>534300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>515300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>542400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>534600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>530600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>509900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>483000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>497700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>459200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>408400</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>415000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>452400</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>444700</v>
+      </c>
+      <c r="E44" s="3">
         <v>433400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>429600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>418100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>449700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>501300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>490100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>502400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>510700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>480700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>444700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>384500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>360100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>347600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>329500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>322700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>346500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>350100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>361500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>332800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>359500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>365600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>360500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>334100</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>344200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>344900</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>319600</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>293500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>272800</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>260400</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>249200</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>234100</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>79100</v>
+      </c>
+      <c r="E45" s="3">
         <v>79500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>71300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>67800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>75200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>76200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>83200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>76500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>83700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>92200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>86900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>69100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>69500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>67100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>67200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>82100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>87000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>84200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>86100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>82500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>76000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>85600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>67600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>52300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>57100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>62900</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>52100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>51400</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>56100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>60100</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>66600</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>80000</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1400700</v>
+      </c>
+      <c r="E46" s="3">
         <v>1317200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1313100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1286000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1352600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1349100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1335400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1406500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1367300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1314200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1295800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1244000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1198700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1126300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1143600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1096700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1220500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1121200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1159100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1122600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1173600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1157700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1170400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1125700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1249200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1279900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1204300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1151000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1084000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1025200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>993000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>1009700</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>25900</v>
+      </c>
+      <c r="E47" s="3">
         <v>24300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>23500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>24400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>24300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>20500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>20400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>22400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>25600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>23700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>23900</v>
-      </c>
-      <c r="N47" s="3">
-        <v>24200</v>
       </c>
       <c r="O47" s="3">
         <v>24200</v>
       </c>
       <c r="P47" s="3">
+        <v>24200</v>
+      </c>
+      <c r="Q47" s="3">
         <v>23300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>22300</v>
-      </c>
-      <c r="R47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="S47" s="3" t="s">
         <v>8</v>
@@ -4173,8 +4277,8 @@
       <c r="U47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V47" s="3">
-        <v>0</v>
+      <c r="V47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W47" s="3">
         <v>0</v>
@@ -4212,204 +4316,213 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>642800</v>
+      </c>
+      <c r="E48" s="3">
         <v>647000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>642300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>652900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>640900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>625800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>590800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>594400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>591100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>601000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>609700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>617800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>626300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>624300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>617100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>705300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>685700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>699100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>685500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>588900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>569800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>552500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>517900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>509300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>511100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>507700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>483800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>484600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>462500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>459700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>466100</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>2771000</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>649900</v>
+      </c>
+      <c r="E49" s="3">
         <v>655300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>651000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>669200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>519100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>446600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>435300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>445600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>410400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>423700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>379800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>384100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>386500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>387400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>379800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>384100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>369100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>378200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>379100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>374000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>383700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>388000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>386700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>274000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>277100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>280200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>277400</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>278700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>268100</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>268800</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>270500</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>306300</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4506,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4604,106 +4720,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>146800</v>
+      </c>
+      <c r="E52" s="3">
         <v>139700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>138700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>138000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>138600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>136600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>130100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>131400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>124800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>128700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>129300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>130100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>118900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>109800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>106600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>58500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>63200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>63700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>59600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>57100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>78800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>68100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>69000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>67600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>57600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>63500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>66900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>65400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>65700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>64000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>64500</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>39700</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4800,106 +4922,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2866100</v>
+      </c>
+      <c r="E54" s="3">
         <v>2783500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2768600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2770500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2675500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2578600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2512000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2600300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2519200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2491300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2438500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2400200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2354600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2271100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2269400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2244600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2338500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2262200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2283300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2142600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2205900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2166300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2144000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>1976600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>2095000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>2131300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>2032400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1979700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>1880300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>1817700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1794100</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1787000</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4934,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4970,596 +5099,615 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>370000</v>
+      </c>
+      <c r="E57" s="3">
         <v>325800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>324900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>304900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>311100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>302100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>320700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>338500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>335800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>324500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>310000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>293900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>268100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>228100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>209400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>187700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>202700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>210100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>229100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>237500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>238700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>226700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>230600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>201300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>201500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>200000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>190600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>194000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>179000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>157800</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>160700</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>143300</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>74400</v>
+      </c>
+      <c r="E58" s="3">
         <v>262100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>284800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>159100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>151600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>4000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>31300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>63900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>41200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>48500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>44500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>22400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>6700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>9500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>58100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>84700</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>110900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>52300</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>50600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>66000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>74000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>43500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>4500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>18100</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>39200</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>73900</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>306900</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>277100</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>245000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>216700</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>290800</v>
+      </c>
+      <c r="E59" s="3">
         <v>305600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>272900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>292400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>249300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>274000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>248400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>287400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>239400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>250100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>230700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>264200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>236200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>249000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>203300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>209600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>172000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>203400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>191100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>193100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>157100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>200400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>183000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>224600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>191700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>216900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>185300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>216200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>169000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>180600</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>157700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>183800</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>735200</v>
+      </c>
+      <c r="E60" s="3">
         <v>893500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>882600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>756400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>712000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>580100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>569300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>629600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>606500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>638500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>581900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>606600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>548800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>499500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>419400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>406800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>432800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>498200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>531100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>482900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>446400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>493100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>487600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>469400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>397700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>435000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>415100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>484100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>654900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>615500</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>563400</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>543800</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>481800</v>
+      </c>
+      <c r="E61" s="3">
         <v>352000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>366600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>496600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>470500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>624800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>600700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>644300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>607200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>553900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>548100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>461000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>454600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>495100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>576300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>617400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>735100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>595800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>596800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>584400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>644400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>632500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>630600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>499600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>687500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>667700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>631700</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>537300</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>298100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>297800</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>324700</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>350200</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>165100</v>
+      </c>
+      <c r="E62" s="3">
         <v>162200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>183300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>196800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>194300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>179500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>187200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>193200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>181900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>182100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>192600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>195500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>197800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>202100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>210200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>216600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>215800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>217000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>227700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>172600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>157300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>155000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>158500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>149800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>173400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>201700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>104600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>103800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>125300</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>123700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>121300</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>121600</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5656,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5754,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5852,106 +6006,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1382100</v>
+      </c>
+      <c r="E66" s="3">
         <v>1407700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1432500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1449800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1376800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1384400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1357200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1467100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1395600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1374500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1322600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1263100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1201200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1196700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1222600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1257500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1399700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1327400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1371700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1255300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1266200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1298900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1294400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1123600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1263300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1309000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1156100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1129600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1082600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1041200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1013500</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1019600</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5986,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6084,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6182,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6280,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6378,106 +6548,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2332500</v>
+      </c>
+      <c r="E72" s="3">
         <v>2219000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2180200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2087800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2056500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1962800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1932800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1849000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1802600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1718000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1700400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1621200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1591200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1507600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1504900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>1445900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>1432800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>1368600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>1361100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>1303200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>1298300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>1223800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1213800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1143400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1089100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1016400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1120200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1056900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1035900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>977300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>977500</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>921800</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6574,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6672,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6770,106 +6952,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1484000</v>
+      </c>
+      <c r="E76" s="3">
         <v>1375800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1336100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1320700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1298700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1194200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1154800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1133200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1123600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1116800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1115900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1137100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1153400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1074400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1046800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>987100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>938800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>934800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>911600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>887300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>939700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>867400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>849600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>853000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>831700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>822300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>876300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>850100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>797700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>776500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>780600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>767400</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6966,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45412</v>
+      </c>
+      <c r="E80" s="2">
         <v>45322</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45230</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45138</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45046</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44957</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44865</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44773</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44681</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44592</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44500</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44408</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44316</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44227</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44135</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44043</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43951</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43861</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43769</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43677</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43585</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43496</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43404</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43312</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43220</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43131</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43039</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42947</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42855</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42766</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42674</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42582</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>113500</v>
+      </c>
+      <c r="E81" s="3">
         <v>98700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>92100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>91900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>93700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>86000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>87200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>101000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>83000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>71800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>77100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>84300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>84400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>56200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>61900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>64100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>63400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>64400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>65000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>58100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>75200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>60100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>73800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>102400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>69900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-52900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>60900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>68200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>60100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>46500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>58000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>59500</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7203,8 +7400,9 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7212,97 +7410,100 @@
         <v>24600</v>
       </c>
       <c r="E83" s="3">
+        <v>24600</v>
+      </c>
+      <c r="F83" s="3">
         <v>24300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>25000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>22500</v>
-      </c>
-      <c r="H83" s="3">
-        <v>22400</v>
       </c>
       <c r="I83" s="3">
         <v>22400</v>
       </c>
       <c r="J83" s="3">
+        <v>22400</v>
+      </c>
+      <c r="K83" s="3">
         <v>22800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>23500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>23700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>23800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>24900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>23800</v>
-      </c>
-      <c r="P83" s="3">
-        <v>23300</v>
       </c>
       <c r="Q83" s="3">
         <v>23300</v>
       </c>
       <c r="R83" s="3">
+        <v>23300</v>
+      </c>
+      <c r="S83" s="3">
         <v>23000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>21800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>21600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>21200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>21300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>20600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>19900</v>
-      </c>
-      <c r="Y83" s="3">
-        <v>19300</v>
       </c>
       <c r="Z83" s="3">
         <v>19300</v>
       </c>
       <c r="AA83" s="3">
+        <v>19300</v>
+      </c>
+      <c r="AB83" s="3">
         <v>19500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>19000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>18900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>19400</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>18500</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>18400</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>18900</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7399,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7497,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7595,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7693,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7791,106 +8004,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>141500</v>
+      </c>
+      <c r="E89" s="3">
         <v>87000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>138000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>190800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>133200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>102300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>118200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>108900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>64100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>36900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>42900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>96300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>103300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>73400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>128900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>121800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>88400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>90700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>86100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>122600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>80400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>79500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>63300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>104200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>48900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>45900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>63900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>87000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>61300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>69800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>99700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>84200</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7925,8 +8144,9 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7934,97 +8154,100 @@
         <v>-21300</v>
       </c>
       <c r="E91" s="3">
+        <v>-21300</v>
+      </c>
+      <c r="F91" s="3">
         <v>-23200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-25700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-35200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-29500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-28100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-28700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-23300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-15200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-18300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-18800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-9800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-11600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-18800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-18200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-26500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-42600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-37100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-38300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-45300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-38900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-28200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-24400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-27300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-25900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-19900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-24700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-32400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-37600</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-12400</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-13500</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8121,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8219,106 +8445,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-23300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-21300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-23200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-172200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-97500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-29500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-28100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-48200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-23300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-64200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-18300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-18100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-9800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-11600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-18800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-22700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-26500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-42600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-37100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-38000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-45300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-38900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-124200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-23100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-27300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-25900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-19100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-43600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-16200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-12600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-23300</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-11300</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8353,52 +8585,53 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-30000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-30100</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-30200</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-30300</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-27900</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-28000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-28200</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-28300</v>
-      </c>
-      <c r="K96" s="3">
-        <v>-27200</v>
       </c>
       <c r="L96" s="3">
         <v>-27200</v>
       </c>
       <c r="M96" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="N96" s="3">
         <v>-27400</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-27700</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-26400</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-26500</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>-26600</v>
       </c>
       <c r="R96" s="3">
         <v>-26600</v>
@@ -8413,22 +8646,22 @@
         <v>-26600</v>
       </c>
       <c r="V96" s="3">
+        <v>-26600</v>
+      </c>
+      <c r="W96" s="3">
         <v>-26800</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-24200</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-24300</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-24400</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-24500</v>
-      </c>
-      <c r="AA96" s="3">
-        <v>-23400</v>
       </c>
       <c r="AB96" s="3">
         <v>-23400</v>
@@ -8437,22 +8670,25 @@
         <v>-23400</v>
       </c>
       <c r="AD96" s="3">
+        <v>-23400</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-22900</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-23200</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-23100</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-23200</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-23300</v>
       </c>
     </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8549,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8647,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8745,298 +8987,310 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-85800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-92800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-78900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-18100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-27300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-64000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-112800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-31400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-37100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-45500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-67800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-84900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-131700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-78900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-195800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>59300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-48300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-14700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-109600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-19700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-55300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>61300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-184700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-61500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-20700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-40000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-46200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-16300</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-55200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-73500</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E101" s="3">
         <v>3100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-5200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>9600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-9600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-4700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-5400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-2900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-1100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-2900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>7200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>2200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>6800</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-5800</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>1300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-2100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-1000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-2800</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>6000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-5200</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-9000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-5000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>13300</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-1700</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>9900</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>2200</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-1600</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-2200</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-3600</v>
       </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>29900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-24000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>30700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>6600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>18400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-32300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>24600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-30400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-22000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>7500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>8000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-62700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>33400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-89900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>115400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>32200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-26000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>12600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-8700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-4800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-112600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-44900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>12600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>41200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>12500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>34100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>19000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-4200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DCI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DCI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="92">
   <si>
     <t>DCI</t>
   </si>
@@ -656,454 +656,480 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45596</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45504</v>
+      </c>
+      <c r="F7" s="2">
         <v>45412</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45322</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45230</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45138</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45046</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44957</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44865</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44773</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44681</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44592</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44500</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44408</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44316</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44227</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44135</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44043</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43951</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43861</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43769</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43677</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>43585</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43496</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43404</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43312</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43220</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43131</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43039</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>42947</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>42855</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>42766</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>42674</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>42582</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>900100</v>
+      </c>
+      <c r="E8" s="3">
+        <v>935400</v>
+      </c>
+      <c r="F8" s="3">
         <v>927900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>876700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>846300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>879500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>875700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>828300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>847300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>890000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>853200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>802500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>760900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>773100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>765000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>679100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>636600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>617400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>629700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>662000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>672700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>727000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>712800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>703700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>701400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>724700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>700000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>664700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>644800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>660100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>608200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>550600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>553000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>593800</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>579400</v>
+      </c>
+      <c r="E9" s="3">
+        <v>596800</v>
+      </c>
+      <c r="F9" s="3">
         <v>597800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>568100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>545400</v>
       </c>
-      <c r="G9" s="3">
-        <v>579400</v>
-      </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
+        <v>576500</v>
+      </c>
+      <c r="J9" s="3">
         <v>586900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>543900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>560100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>598400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>584200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>552700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>501400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>507400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>507000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>448000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>413900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>409500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>420500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>438800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>441400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>483200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>472100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>478300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>463000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>471700</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>460400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>445800</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>420500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>430600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>396700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>362700</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>358800</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AK9" s="3">
         <v>384500</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>320700</v>
+      </c>
+      <c r="E10" s="3">
+        <v>338600</v>
+      </c>
+      <c r="F10" s="3">
         <v>330100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>308600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>300900</v>
       </c>
-      <c r="G10" s="3">
-        <v>300100</v>
-      </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
+        <v>303000</v>
+      </c>
+      <c r="J10" s="3">
         <v>288800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>284400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>287200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>291600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>269000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>249800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>259500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>265700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>258000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>231100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>222700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>207900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>209200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>223200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>231300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>243800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>240700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>225400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>238400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>253000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>239600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>218900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>224300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>229500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>211500</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>187900</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>194200</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AK10" s="3">
         <v>209300</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1139,37 +1165,39 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>22700</v>
+      </c>
+      <c r="E12" s="3">
+        <v>25400</v>
+      </c>
+      <c r="F12" s="3">
         <v>24800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>22100</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>21300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>21900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>19000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>18500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>18700</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>8</v>
@@ -1240,8 +1268,14 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1341,16 +1375,22 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E14" s="3">
+        <v>6400</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>8</v>
@@ -1361,8 +1401,8 @@
       <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
+      <c r="I14" s="3">
+        <v>21800</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>8</v>
@@ -1376,23 +1416,23 @@
       <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N14" s="3">
+      <c r="N14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="3">
         <v>2500</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q14" s="3">
-        <v>14800</v>
+        <v>0</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>8</v>
+      <c r="S14" s="3">
+        <v>14800</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>8</v>
@@ -1403,11 +1443,11 @@
       <c r="V14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
@@ -1442,40 +1482,46 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>3900</v>
+        <v>25500</v>
       </c>
       <c r="E15" s="3">
-        <v>3800</v>
+        <v>24900</v>
       </c>
       <c r="F15" s="3">
-        <v>4000</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>8</v>
+        <v>24600</v>
+      </c>
+      <c r="G15" s="3">
+        <v>24600</v>
+      </c>
+      <c r="H15" s="3">
+        <v>24300</v>
+      </c>
+      <c r="I15" s="3">
+        <v>25000</v>
+      </c>
+      <c r="J15" s="3">
+        <v>22500</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
-      <c r="M15" s="3">
-        <v>0</v>
+      <c r="L15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1543,8 +1589,14 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,210 +1629,224 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>784300</v>
+        <v>768200</v>
       </c>
       <c r="E17" s="3">
-        <v>747000</v>
+        <v>783900</v>
       </c>
       <c r="F17" s="3">
-        <v>721700</v>
+        <v>786500</v>
       </c>
       <c r="G17" s="3">
-        <v>758900</v>
+        <v>746100</v>
       </c>
       <c r="H17" s="3">
-        <v>751700</v>
+        <v>720900</v>
       </c>
       <c r="I17" s="3">
+        <v>738000</v>
+      </c>
+      <c r="J17" s="3">
+        <v>753400</v>
+      </c>
+      <c r="K17" s="3">
         <v>712000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>728000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>760700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>742200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>706800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>653400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>661100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>655600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>603000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>549400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>534900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>545200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>577500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>584000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>622600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>612800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>618600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>602700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>620900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>599100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>583100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>554100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>565800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>519700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>481200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>476600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>503700</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>143600</v>
+        <v>131900</v>
       </c>
       <c r="E18" s="3">
-        <v>129700</v>
+        <v>151500</v>
       </c>
       <c r="F18" s="3">
-        <v>124600</v>
+        <v>141400</v>
       </c>
       <c r="G18" s="3">
-        <v>120600</v>
+        <v>130600</v>
       </c>
       <c r="H18" s="3">
-        <v>124000</v>
+        <v>125400</v>
       </c>
       <c r="I18" s="3">
+        <v>141500</v>
+      </c>
+      <c r="J18" s="3">
+        <v>122300</v>
+      </c>
+      <c r="K18" s="3">
         <v>116300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>119300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>129300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>111000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>95700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>107500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>112000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>109400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>76100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>87200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>82500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>84500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>84500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>88700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>104400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>100000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>85100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>98700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>103800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>100900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>81600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>90700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>94300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>88500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>69400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>76400</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>90100</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1816,513 +1882,545 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>5400</v>
+        <v>-5200</v>
       </c>
       <c r="E20" s="3">
-        <v>4900</v>
+        <v>400</v>
       </c>
       <c r="F20" s="3">
-        <v>3800</v>
+        <v>-7600</v>
       </c>
       <c r="G20" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="H20" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="K20" s="3">
         <v>1600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="L20" s="3">
+        <v>1800</v>
+      </c>
+      <c r="M20" s="3">
+        <v>3400</v>
+      </c>
+      <c r="N20" s="3">
+        <v>4100</v>
+      </c>
+      <c r="O20" s="3">
+        <v>2400</v>
+      </c>
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>5100</v>
+      </c>
+      <c r="R20" s="3">
+        <v>4700</v>
+      </c>
+      <c r="S20" s="3">
+        <v>1100</v>
+      </c>
+      <c r="T20" s="3">
+        <v>-1500</v>
+      </c>
+      <c r="U20" s="3">
+        <v>2700</v>
+      </c>
+      <c r="V20" s="3">
+        <v>4300</v>
+      </c>
+      <c r="W20" s="3">
+        <v>2800</v>
+      </c>
+      <c r="X20" s="3">
         <v>2600</v>
       </c>
-      <c r="I20" s="3">
-        <v>1600</v>
-      </c>
-      <c r="J20" s="3">
-        <v>1800</v>
-      </c>
-      <c r="K20" s="3">
-        <v>3400</v>
-      </c>
-      <c r="L20" s="3">
-        <v>4100</v>
-      </c>
-      <c r="M20" s="3">
-        <v>2400</v>
-      </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3">
-        <v>5100</v>
-      </c>
-      <c r="P20" s="3">
+      <c r="Y20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="Z20" s="3">
         <v>4700</v>
       </c>
-      <c r="Q20" s="3">
-        <v>1100</v>
-      </c>
-      <c r="R20" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="S20" s="3">
-        <v>2700</v>
-      </c>
-      <c r="T20" s="3">
-        <v>4300</v>
-      </c>
-      <c r="U20" s="3">
-        <v>2800</v>
-      </c>
-      <c r="V20" s="3">
-        <v>2600</v>
-      </c>
-      <c r="W20" s="3">
-        <v>-400</v>
-      </c>
-      <c r="X20" s="3">
-        <v>4700</v>
-      </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>1900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>5300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>3500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>-100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>-800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>2500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>1700</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AJ20" s="3">
         <v>8100</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AK20" s="3">
         <v>-2700</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>162600</v>
+      </c>
+      <c r="E21" s="3">
+        <v>176000</v>
+      </c>
+      <c r="F21" s="3">
         <v>173600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>159200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>152700</v>
       </c>
-      <c r="G21" s="3">
-        <v>147200</v>
-      </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
+        <v>169000</v>
+      </c>
+      <c r="J21" s="3">
         <v>149100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>140300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>143500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>155500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>138600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>121800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>131300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>142000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>137900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>100500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>109000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>108200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>110600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>108900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>112500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>125300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>125300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>105700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>119900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>128400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>123900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>100500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>108800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>116200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>107600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>89500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>103400</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>106400</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E22" s="3">
+        <v>5300</v>
+      </c>
+      <c r="F22" s="3">
         <v>5000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>5600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>5500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>4900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>5100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>4600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>4500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>4100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>3800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>3600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>3400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>3100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>3200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>3300</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>3500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>3900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>4400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>4500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>4700</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>5200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>5200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>5300</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>4200</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>5600</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>5400</v>
-      </c>
-      <c r="AC22" s="3">
-        <v>5100</v>
-      </c>
-      <c r="AD22" s="3">
-        <v>5200</v>
       </c>
       <c r="AE22" s="3">
         <v>5100</v>
       </c>
       <c r="AF22" s="3">
-        <v>4800</v>
+        <v>5200</v>
       </c>
       <c r="AG22" s="3">
-        <v>4800</v>
+        <v>5100</v>
       </c>
       <c r="AH22" s="3">
         <v>4800</v>
       </c>
       <c r="AI22" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AJ22" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AK22" s="3">
         <v>4900</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>130500</v>
+      </c>
+      <c r="E23" s="3">
+        <v>139400</v>
+      </c>
+      <c r="F23" s="3">
         <v>144000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>129000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>122900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>117300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>121500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>113300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>116600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>128600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>111300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>94500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>104100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>114000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>110900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>73900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>82200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>81300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>84400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>82800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>86600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>98800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>99500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>80500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>96400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>103500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>99000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>76400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>84700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>91700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>84300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>66300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>79700</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>82500</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>31500</v>
+      </c>
+      <c r="E24" s="3">
+        <v>29700</v>
+      </c>
+      <c r="F24" s="3">
         <v>30500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>30300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>30800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>25400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>27800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>27300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>29400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>27600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>28300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>22700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>27000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>29700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>26500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>17700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>20300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>17200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>21000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>18400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>21600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>21600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>24300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>20000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>23500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>27100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>28700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>119000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>23800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>23500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>24200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>19800</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AJ24" s="3">
         <v>21700</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AK24" s="3">
         <v>23000</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,210 +2520,228 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>99000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>109700</v>
+      </c>
+      <c r="F26" s="3">
         <v>113500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>98700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>92100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>91900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>93700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>86000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>87200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>101000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>83000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>71800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>77100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>84300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>84400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>56200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>61900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>64100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>63400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>64400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>65000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>77200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>75200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>60500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>72900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>76400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>70300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>-42600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>60900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>68200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>60100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>46500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>58000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>59500</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>99000</v>
+      </c>
+      <c r="E27" s="3">
+        <v>109700</v>
+      </c>
+      <c r="F27" s="3">
         <v>113500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>98700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>92100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>91900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>93700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>86000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>87200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>101000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>83000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>71800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>77100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>84300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>84400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>56200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>61900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>64100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>63400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>64400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>65000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>77200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>75200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>60500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>72900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>76400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>70300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>-42600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>60900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>68200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>60100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>46500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>58000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>59500</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,8 +2841,14 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2766,11 +2888,11 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q29" s="3" t="s">
-        <v>8</v>
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>0</v>
       </c>
       <c r="R29" s="3" t="s">
         <v>8</v>
@@ -2787,32 +2909,32 @@
       <c r="V29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W29" s="3">
+      <c r="W29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y29" s="3">
         <v>-19100</v>
       </c>
-      <c r="X29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
         <v>-400</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AB29" s="3">
         <v>900</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AC29" s="3">
         <v>26000</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AD29" s="3">
         <v>-400</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AE29" s="3">
         <v>-10300</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
@@ -2826,8 +2948,14 @@
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +3055,14 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,210 +3162,228 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-5400</v>
+        <v>5200</v>
       </c>
       <c r="E32" s="3">
-        <v>-4900</v>
+        <v>-400</v>
       </c>
       <c r="F32" s="3">
-        <v>-3800</v>
+        <v>7600</v>
       </c>
       <c r="G32" s="3">
+        <v>4000</v>
+      </c>
+      <c r="H32" s="3">
+        <v>3000</v>
+      </c>
+      <c r="I32" s="3">
+        <v>2500</v>
+      </c>
+      <c r="J32" s="3">
+        <v>4300</v>
+      </c>
+      <c r="K32" s="3">
         <v>-1600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="L32" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="M32" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="N32" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="O32" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="R32" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="S32" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="T32" s="3">
+        <v>1500</v>
+      </c>
+      <c r="U32" s="3">
+        <v>-2700</v>
+      </c>
+      <c r="V32" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="W32" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="X32" s="3">
         <v>-2600</v>
       </c>
-      <c r="I32" s="3">
-        <v>-1600</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-1800</v>
-      </c>
-      <c r="K32" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="L32" s="3">
-        <v>-4100</v>
-      </c>
-      <c r="M32" s="3">
-        <v>-2400</v>
-      </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-5100</v>
-      </c>
-      <c r="P32" s="3">
+      <c r="Y32" s="3">
+        <v>400</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q32" s="3">
-        <v>-1100</v>
-      </c>
-      <c r="R32" s="3">
-        <v>1500</v>
-      </c>
-      <c r="S32" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="T32" s="3">
-        <v>-4300</v>
-      </c>
-      <c r="U32" s="3">
-        <v>-2800</v>
-      </c>
-      <c r="V32" s="3">
-        <v>-2600</v>
-      </c>
-      <c r="W32" s="3">
-        <v>400</v>
-      </c>
-      <c r="X32" s="3">
-        <v>-4700</v>
-      </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-5300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>-3500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-2500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>-600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>-1700</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AJ32" s="3">
         <v>-8100</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AK32" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>99000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>109700</v>
+      </c>
+      <c r="F33" s="3">
         <v>113500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>98700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>92100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>91900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>93700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>86000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>87200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>101000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>83000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>71800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>77100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>84300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>84400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>56200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>61900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>64100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>63400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>64400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>65000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>58100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>75200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>60100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>73800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>102400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>69900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>-52900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>60900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>68200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>60100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>46500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>58000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>59500</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,215 +3483,233 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>99000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>109700</v>
+      </c>
+      <c r="F35" s="3">
         <v>113500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>98700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>92100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>91900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>93700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>86000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>87200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>101000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>83000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>71800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>77100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>84300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>84400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>56200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>61900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>64100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>63400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>64400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>65000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>58100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>75200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>60100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>73800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>102400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>69900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>-52900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>60900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>68200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>60100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>46500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>58000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>59500</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45596</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45504</v>
+      </c>
+      <c r="F38" s="2">
         <v>45412</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45322</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45230</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45138</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45046</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44957</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44865</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44773</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44681</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44592</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44500</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44408</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44316</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44227</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44135</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44043</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43951</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43861</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43769</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43677</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>43585</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43496</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43404</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43312</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43220</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43131</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43039</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>42947</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>42855</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>42766</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>42674</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>42582</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3745,10 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,109 +3784,117 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>221200</v>
+      </c>
+      <c r="E41" s="3">
+        <v>232700</v>
+      </c>
+      <c r="F41" s="3">
         <v>223700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>193800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>217800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>187100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>186000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>179400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>161000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>193300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>168700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>170400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>200800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>222800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>215300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>207300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>270000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>236600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>326500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>211100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>210000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>177800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>203800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>191200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>199900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>204700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>317300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>362200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>349600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>308400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>295900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>296300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>262200</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>243200</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3814,465 +3994,495 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>631300</v>
+      </c>
+      <c r="E43" s="3">
+        <v>645600</v>
+      </c>
+      <c r="F43" s="3">
         <v>653200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>610500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>594400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>613000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>641700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>592200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>601100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>634300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>604200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>570900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>563400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>567600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>553800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>504300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>476900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>455300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>460500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>475800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>501500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>529500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>534300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>515300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>542400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>534600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>530600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>509900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>483000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>497700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>459200</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>408400</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AJ43" s="3">
         <v>415000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AK43" s="3">
         <v>452400</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>520000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>476700</v>
+      </c>
+      <c r="F44" s="3">
         <v>444700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>433400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>429600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>418100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>449700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>501300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>490100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>502400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>510700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>480700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>444700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>384500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>360100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>347600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>329500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>322700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>346500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>350100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>361500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>332800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>359500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>365600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>360500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>334100</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>344200</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>344900</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>319600</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>293500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>272800</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AI44" s="3">
         <v>260400</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AJ44" s="3">
         <v>249200</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AK44" s="3">
         <v>234100</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>79100</v>
-      </c>
-      <c r="E45" s="3">
-        <v>79500</v>
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F45" s="3">
-        <v>71300</v>
+        <v>1100</v>
       </c>
       <c r="G45" s="3">
-        <v>67800</v>
+        <v>1200</v>
       </c>
       <c r="H45" s="3">
-        <v>75200</v>
-      </c>
-      <c r="I45" s="3">
+        <v>2300</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" s="3">
+        <v>1800</v>
+      </c>
+      <c r="K45" s="3">
         <v>76200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>83200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>76500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>83700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>92200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>86900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>69100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>69500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>67100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>67200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>82100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>87000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>84200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>86100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>82500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>76000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>85600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>67600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>52300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>57100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>62900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>52100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>51400</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>56100</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>60100</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AJ45" s="3">
         <v>66600</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AK45" s="3">
         <v>80000</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1479400</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1438100</v>
+      </c>
+      <c r="F46" s="3">
         <v>1400700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>1317200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>1313100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>1286000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>1352600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>1349100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>1335400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>1406500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>1367300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>1314200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>1295800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>1244000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>1198700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>1126300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>1143600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>1096700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>1220500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>1121200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>1159100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>1122600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>1173600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>1157700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>1170400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>1125700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>1249200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>1279900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>1204300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>1151000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>1084000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>1025200</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>993000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AK46" s="3">
         <v>1009700</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3">
+        <v>26900</v>
+      </c>
+      <c r="F47" s="3">
         <v>25900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>24300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>23500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>24400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>24300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>20500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>20400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>22400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>25600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>23700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>23900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>24200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>24200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>23300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>22300</v>
-      </c>
-      <c r="S47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="U47" s="3" t="s">
         <v>8</v>
@@ -4280,11 +4490,11 @@
       <c r="V47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W47" s="3">
-        <v>0</v>
-      </c>
-      <c r="X47" s="3">
-        <v>0</v>
+      <c r="W47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y47" s="3">
         <v>0</v>
@@ -4319,210 +4529,228 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>647400</v>
+      </c>
+      <c r="E48" s="3">
+        <v>705200</v>
+      </c>
+      <c r="F48" s="3">
         <v>642800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>647000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>642300</v>
       </c>
-      <c r="G48" s="3">
-        <v>652900</v>
-      </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
+        <v>712300</v>
+      </c>
+      <c r="J48" s="3">
         <v>640900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>625800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>590800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>594400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>591100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>601000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>609700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>617800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>626300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>624300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>617100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>705300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>685700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>699100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>685500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>588900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>569800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>552500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>517900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>509300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>511100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>507700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>483800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>484600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>462500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>459700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AJ48" s="3">
         <v>466100</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AK48" s="3">
         <v>2771000</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>648200</v>
+      </c>
+      <c r="E49" s="3">
+        <v>650300</v>
+      </c>
+      <c r="F49" s="3">
         <v>649900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>655300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>651000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>669200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>519100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>446600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>435300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>445600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>410400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>423700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>379800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>384100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>386500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>387400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>379800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>384100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>369100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>378200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>379100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>374000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>383700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>388000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>386700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>274000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>277100</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>280200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>277400</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>278700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>268100</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AI49" s="3">
         <v>268800</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AJ49" s="3">
         <v>270500</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AK49" s="3">
         <v>306300</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4850,14 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,109 +4957,121 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>268600</v>
+      </c>
+      <c r="E52" s="3">
+        <v>93800</v>
+      </c>
+      <c r="F52" s="3">
         <v>146800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>139700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>138700</v>
       </c>
-      <c r="G52" s="3">
-        <v>138000</v>
-      </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
+        <v>78600</v>
+      </c>
+      <c r="J52" s="3">
         <v>138600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>136600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>130100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>131400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>124800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>128700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>129300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>130100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>118900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>109800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>106600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>58500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>63200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>63700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>59600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>57100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>78800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>68100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>69000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>67600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>57600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>63500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>66900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>65400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>65700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>64000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AJ52" s="3">
         <v>64500</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AK52" s="3">
         <v>39700</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,109 +5171,121 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3043600</v>
+      </c>
+      <c r="E54" s="3">
+        <v>2914300</v>
+      </c>
+      <c r="F54" s="3">
         <v>2866100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>2783500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>2768600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>2770500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>2675500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>2578600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>2512000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>2600300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>2519200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>2491300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>2438500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>2400200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>2354600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>2271100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>2269400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>2244600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>2338500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>2262200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>2283300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>2142600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>2205900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>2166300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>2144000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>1976600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>2095000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>2131300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>2032400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>1979700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>1880300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>1817700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>1794100</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>1787000</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5321,10 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,614 +5360,652 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>373500</v>
+      </c>
+      <c r="E57" s="3">
+        <v>379400</v>
+      </c>
+      <c r="F57" s="3">
         <v>370000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>325800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>324900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>304900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>311100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>302100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>320700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>338500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>335800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>324500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>310000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>293900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>268100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>228100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>209400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>187700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>202700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>210100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>229100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>237500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>238700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>226700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>230600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>201300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>201500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>200000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>190600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>194000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>179000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>157800</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>160700</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AK57" s="3">
         <v>143300</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>103200</v>
+      </c>
+      <c r="E58" s="3">
+        <v>73500</v>
+      </c>
+      <c r="F58" s="3">
         <v>74400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>262100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>284800</v>
       </c>
-      <c r="G58" s="3">
-        <v>159100</v>
-      </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
+        <v>176900</v>
+      </c>
+      <c r="J58" s="3">
         <v>151600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>4000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>3700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>31300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>63900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>41200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>48500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>44500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>22400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>6700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>9500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>58100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>84700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>110900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>52300</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>50600</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>66000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>74000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>43500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>4500</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>18100</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>39200</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>73900</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>306900</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AI58" s="3">
         <v>277100</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AJ58" s="3">
         <v>245000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AK58" s="3">
         <v>216700</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>290800</v>
+        <v>188600</v>
       </c>
       <c r="E59" s="3">
-        <v>305600</v>
+        <v>187200</v>
       </c>
       <c r="F59" s="3">
-        <v>272900</v>
+        <v>167600</v>
       </c>
       <c r="G59" s="3">
-        <v>292400</v>
+        <v>195300</v>
       </c>
       <c r="H59" s="3">
-        <v>249300</v>
+        <v>162700</v>
       </c>
       <c r="I59" s="3">
+        <v>153500</v>
+      </c>
+      <c r="J59" s="3">
+        <v>143500</v>
+      </c>
+      <c r="K59" s="3">
         <v>274000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>248400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>287400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>239400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>250100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>230700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>264200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>236200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>249000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>203300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>209600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>172000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>203400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>191100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>193100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>157100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>200400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>183000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>224600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>191700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>216900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>185300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>216200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>169000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>180600</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>157700</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AK59" s="3">
         <v>183800</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>800600</v>
+      </c>
+      <c r="E60" s="3">
+        <v>782500</v>
+      </c>
+      <c r="F60" s="3">
         <v>735200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>893500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>882600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>756400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>712000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>580100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>569300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>629600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>606500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>638500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>581900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>606600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>548800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>499500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>419400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>406800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>432800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>498200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>531100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>482900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>446400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>493100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>487600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>469400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>397700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>435000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>415100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>484100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>654900</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>615500</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AJ60" s="3">
         <v>563400</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AK60" s="3">
         <v>543800</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>538600</v>
+      </c>
+      <c r="E61" s="3">
+        <v>524700</v>
+      </c>
+      <c r="F61" s="3">
         <v>481800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>352000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>366600</v>
       </c>
-      <c r="G61" s="3">
-        <v>496600</v>
-      </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
+        <v>539000</v>
+      </c>
+      <c r="J61" s="3">
         <v>470500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>624800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>600700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>644300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>607200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>553900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>548100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>461000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>454600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>495100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>576300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>617400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>735100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>595800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>596800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>584400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>644400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>632500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>630600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>499600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>687500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>667700</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>631700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>537300</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>298100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AI61" s="3">
         <v>297800</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AJ61" s="3">
         <v>324700</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AK61" s="3">
         <v>350200</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>165100</v>
+        <v>146100</v>
       </c>
       <c r="E62" s="3">
-        <v>162200</v>
+        <v>77200</v>
       </c>
       <c r="F62" s="3">
-        <v>183300</v>
+        <v>147600</v>
       </c>
       <c r="G62" s="3">
-        <v>196800</v>
+        <v>140300</v>
       </c>
       <c r="H62" s="3">
-        <v>194300</v>
+        <v>155900</v>
       </c>
       <c r="I62" s="3">
+        <v>104000</v>
+      </c>
+      <c r="J62" s="3">
+        <v>161600</v>
+      </c>
+      <c r="K62" s="3">
         <v>179500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>187200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>193200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>181900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>182100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>192600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>195500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>197800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>202100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>210200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>216600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>215800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>217000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>227700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>172600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>157300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>155000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>158500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>149800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>173400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>201700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>104600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>103800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>125300</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>123700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AJ62" s="3">
         <v>121300</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AK62" s="3">
         <v>121600</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +6105,14 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6212,14 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,109 +6319,121 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1500600</v>
+      </c>
+      <c r="E66" s="3">
+        <v>1425200</v>
+      </c>
+      <c r="F66" s="3">
         <v>1382100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>1407700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>1432500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>1449800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>1376800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>1384400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>1357200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>1467100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>1395600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>1374500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>1322600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>1263100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>1201200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>1196700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>1222600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>1257500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>1399700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>1327400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>1371700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>1255300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>1266200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>1298900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>1294400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>1123600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>1263300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>1309000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>1156100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>1129600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>1082600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>1041200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>1013500</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>1019600</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6469,10 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6572,14 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6679,14 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6450,8 +6786,14 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,109 +6893,121 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E72" s="3">
+        <v>2377500</v>
+      </c>
+      <c r="F72" s="3">
         <v>2332500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>2219000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>2180200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>2087800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>2056500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>1962800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>1932800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>1849000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>1802600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>1718000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>1700400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>1621200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>1591200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>1507600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>1504900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>1445900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>1432800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>1368600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>1361100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>1303200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>1298300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>1223800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>1213800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>1143400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>1089100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>1016400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>1120200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>1056900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>1035900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>977300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>977500</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>921800</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +7107,14 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7214,14 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,109 +7321,121 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1543000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>1489100</v>
+      </c>
+      <c r="F76" s="3">
         <v>1484000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>1375800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>1336100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>1320700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>1298700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>1194200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>1154800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>1133200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>1123600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>1116800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>1115900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>1137100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>1153400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>1074400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>1046800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>987100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>938800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>934800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>911600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>887300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>939700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>867400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>849600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>853000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>831700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>822300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>876300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>850100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>797700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>776500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>780600</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>767400</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,215 +7535,233 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45596</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45504</v>
+      </c>
+      <c r="F80" s="2">
         <v>45412</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45322</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45230</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45138</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45046</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44957</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44865</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44773</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44681</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44592</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44500</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44408</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44316</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44227</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44135</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44043</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43951</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43861</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43769</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43677</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>43585</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43496</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43404</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43312</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43220</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43131</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43039</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>42947</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>42855</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>42766</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>42674</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>42582</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>99000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>109700</v>
+      </c>
+      <c r="F81" s="3">
         <v>113500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>98700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>92100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>91900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>93700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>86000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>87200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>101000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>83000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>71800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>77100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>84300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>84400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>56200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>61900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>64100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>63400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>64400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>65000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>58100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>75200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>60100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>73800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>102400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>69900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>-52900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>60900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>68200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>60100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>46500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>58000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>59500</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,109 +7797,117 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>24600</v>
+        <v>20300</v>
       </c>
       <c r="E83" s="3">
-        <v>24600</v>
+        <v>21600</v>
       </c>
       <c r="F83" s="3">
-        <v>24300</v>
+        <v>19600</v>
       </c>
       <c r="G83" s="3">
-        <v>25000</v>
+        <v>19800</v>
       </c>
       <c r="H83" s="3">
-        <v>22500</v>
+        <v>19900</v>
       </c>
       <c r="I83" s="3">
+        <v>20500</v>
+      </c>
+      <c r="J83" s="3">
+        <v>21100</v>
+      </c>
+      <c r="K83" s="3">
         <v>22400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>22400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>22800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>23500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>23700</v>
-      </c>
-      <c r="N83" s="3">
-        <v>23800</v>
-      </c>
-      <c r="O83" s="3">
-        <v>24900</v>
       </c>
       <c r="P83" s="3">
         <v>23800</v>
       </c>
       <c r="Q83" s="3">
+        <v>24900</v>
+      </c>
+      <c r="R83" s="3">
+        <v>23800</v>
+      </c>
+      <c r="S83" s="3">
         <v>23300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>23300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>23000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>21800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>21600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>21200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>21300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>20600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>19900</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>19300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>19300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>19500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>19000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>18900</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>19400</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>18500</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AI83" s="3">
         <v>18400</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AJ83" s="3">
         <v>18900</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AK83" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +8007,14 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +8114,14 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8221,14 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8328,14 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,109 +8435,121 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>72900</v>
+      </c>
+      <c r="E89" s="3">
+        <v>126000</v>
+      </c>
+      <c r="F89" s="3">
         <v>141500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>87000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>138000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>190800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>133200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>102300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>118200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>108900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>64100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>36900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>42900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>96300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>103300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>73400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>128900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>121800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>88400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>90700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>86100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>122600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>80400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>79500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>63300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>104200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>48900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>45900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>63900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>87000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>61300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>69800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>99700</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>84200</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,109 +8585,117 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-25000</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-19800</v>
+      </c>
+      <c r="F91" s="3">
         <v>-21300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-21300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-23200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-25700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-35200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-29500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-28100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-28700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-23300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-15200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-18300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-18800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-9800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-11600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-18800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-18200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-26500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-42600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-37100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-38300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-45300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-38900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-28200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-24400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-27300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-25900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-19900</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-24700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-32400</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AI91" s="3">
         <v>-37600</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AJ91" s="3">
         <v>-12400</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AK91" s="3">
         <v>-13500</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8795,14 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,109 +8902,121 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-96000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-19100</v>
+      </c>
+      <c r="F94" s="3">
         <v>-23300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-21300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-23200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-172200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-97500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-29500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-28100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-48200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-23300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-64200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-18300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-18100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-9800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-11600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-18800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-22700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-26500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-42600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-37100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-38000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-45300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-38900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-124200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-23100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-27300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-25900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-19100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-43600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-16200</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>-12600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AJ94" s="3">
         <v>-23300</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AK94" s="3">
         <v>-11300</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,58 +9052,60 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-30000</v>
+        <v>32400</v>
       </c>
       <c r="E96" s="3">
-        <v>-30100</v>
+        <v>32500</v>
       </c>
       <c r="F96" s="3">
-        <v>-30200</v>
+        <v>30000</v>
       </c>
       <c r="G96" s="3">
-        <v>-30300</v>
+        <v>30100</v>
       </c>
       <c r="H96" s="3">
-        <v>-27900</v>
+        <v>30200</v>
       </c>
       <c r="I96" s="3">
+        <v>30300</v>
+      </c>
+      <c r="J96" s="3">
+        <v>27900</v>
+      </c>
+      <c r="K96" s="3">
         <v>-28000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>-28200</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>-28300</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>-27200</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>-27200</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>-27400</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>-27700</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>-26400</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>-26500</v>
-      </c>
-      <c r="R96" s="3">
-        <v>-26600</v>
-      </c>
-      <c r="S96" s="3">
-        <v>-26600</v>
       </c>
       <c r="T96" s="3">
         <v>-26600</v>
@@ -8649,46 +9117,52 @@
         <v>-26600</v>
       </c>
       <c r="W96" s="3">
+        <v>-26600</v>
+      </c>
+      <c r="X96" s="3">
+        <v>-26600</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-26800</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Z96" s="3">
         <v>-24200</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="AA96" s="3">
         <v>-24300</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AB96" s="3">
         <v>-24400</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AC96" s="3">
         <v>-24500</v>
-      </c>
-      <c r="AB96" s="3">
-        <v>-23400</v>
-      </c>
-      <c r="AC96" s="3">
-        <v>-23400</v>
       </c>
       <c r="AD96" s="3">
         <v>-23400</v>
       </c>
       <c r="AE96" s="3">
+        <v>-23400</v>
+      </c>
+      <c r="AF96" s="3">
+        <v>-23400</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-22900</v>
-      </c>
-      <c r="AF96" s="3">
-        <v>-23200</v>
-      </c>
-      <c r="AG96" s="3">
-        <v>-23100</v>
       </c>
       <c r="AH96" s="3">
         <v>-23200</v>
       </c>
       <c r="AI96" s="3">
+        <v>-23100</v>
+      </c>
+      <c r="AJ96" s="3">
+        <v>-23200</v>
+      </c>
+      <c r="AK96" s="3">
         <v>-23300</v>
       </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9262,14 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9369,14 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,307 +9476,331 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-98400</v>
+      </c>
+      <c r="F100" s="3">
         <v>-85800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-92800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-78900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-18100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-27300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-64000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-112800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-31400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-37100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-45500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-67800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-84900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-131700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-78900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-195800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>59300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-48300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-14700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-109600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-19700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-55300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>61300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-184700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-61500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-20700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-1900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>-40000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>-46200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>-16300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>-55200</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AK100" s="3">
         <v>-73500</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-2500</v>
+        <v>-5200</v>
       </c>
       <c r="E101" s="3">
-        <v>3100</v>
+        <v>600</v>
       </c>
       <c r="F101" s="3">
-        <v>-5200</v>
+        <v>-1800</v>
       </c>
       <c r="G101" s="3">
-        <v>600</v>
+        <v>9600</v>
       </c>
       <c r="H101" s="3">
-        <v>-1800</v>
+        <v>-9600</v>
       </c>
       <c r="I101" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="J101" s="3">
+        <v>-5400</v>
+      </c>
+      <c r="K101" s="3">
         <v>9600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-9600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-4700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-5400</v>
-      </c>
-      <c r="M101" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="N101" s="3">
-        <v>-1100</v>
       </c>
       <c r="O101" s="3">
         <v>-2900</v>
       </c>
       <c r="P101" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="Q101" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="R101" s="3">
         <v>-600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>7200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>2200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>6800</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>-5800</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>1300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>-2100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>-1000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>-2800</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>6000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>-5200</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>-9000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>-5000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>13300</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>-1700</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AG101" s="3">
         <v>9900</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AH101" s="3">
         <v>2200</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AI101" s="3">
         <v>-1600</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AJ101" s="3">
         <v>-2200</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AK101" s="3">
         <v>-3600</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-11500</v>
+      </c>
+      <c r="E102" s="3">
+        <v>9000</v>
+      </c>
+      <c r="F102" s="3">
         <v>29900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-24000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>30700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>1100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>6600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>18400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-32300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>24600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-1700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-30400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-22000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>7500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>8000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-62700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>33400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-89900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>115400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>1100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>32200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>-26000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>12600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-8700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-4800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>-112600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-44900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>12600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>41200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>12500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>-400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>34100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>19000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>-4200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DCI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DCI_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="92">
   <si>
     <t>DCI</t>
   </si>
@@ -656,480 +656,493 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E7" s="2">
         <v>45596</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45504</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45412</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45322</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45230</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45138</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45046</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44957</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44865</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44773</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44681</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44592</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44500</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44408</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44316</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44227</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44135</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44043</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43951</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43861</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43769</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43677</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43585</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43496</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43404</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43312</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43220</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43131</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43039</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42947</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42855</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42766</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42674</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42582</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>870000</v>
+      </c>
+      <c r="E8" s="3">
         <v>900100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>935400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>927900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>876700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>846300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>879500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>875700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>828300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>847300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>890000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>853200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>802500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>760900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>773100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>765000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>679100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>636600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>617400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>629700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>662000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>672700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>727000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>712800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>703700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>701400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>724700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>700000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>664700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>644800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>660100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>608200</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>550600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>553000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>593800</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>563500</v>
+      </c>
+      <c r="E9" s="3">
         <v>579400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>596800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>597800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>568100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>545400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>576500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>586900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>543900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>560100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>598400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>584200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>552700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>501400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>507400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>507000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>448000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>413900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>409500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>420500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>438800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>441400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>483200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>472100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>478300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>463000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>471700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>460400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>445800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>420500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>430600</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>396700</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>362700</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>358800</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>384500</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>306500</v>
+      </c>
+      <c r="E10" s="3">
         <v>320700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>338600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>330100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>308600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>300900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>303000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>288800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>284400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>287200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>291600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>269000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>249800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>259500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>265700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>258000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>231100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>222700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>207900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>209200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>223200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>231300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>243800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>240700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>225400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>238400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>253000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>239600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>218900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>224300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>229500</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>211500</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>187900</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>194200</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>209300</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1167,40 +1180,41 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>21200</v>
+      </c>
+      <c r="E12" s="3">
         <v>22700</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>25400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>24800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>22100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>21300</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>21900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>19000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>18500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>18700</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N12" s="3" t="s">
         <v>8</v>
@@ -1274,8 +1288,11 @@
       <c r="AK12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1381,19 +1398,22 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>1100</v>
+        <v>2200</v>
       </c>
       <c r="E14" s="3">
+        <v>3300</v>
+      </c>
+      <c r="F14" s="3">
         <v>6400</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>8</v>
@@ -1401,11 +1421,11 @@
       <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3">
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3">
         <v>21800</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
@@ -1422,20 +1442,20 @@
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="3">
         <v>2500</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3" t="s">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>14800</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>8</v>
@@ -1449,8 +1469,8 @@
       <c r="X14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
@@ -1488,34 +1508,37 @@
       <c r="AK14" s="3">
         <v>0</v>
       </c>
+      <c r="AL14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E15" s="3">
         <v>25500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>24900</v>
-      </c>
-      <c r="F15" s="3">
-        <v>24600</v>
       </c>
       <c r="G15" s="3">
         <v>24600</v>
       </c>
       <c r="H15" s="3">
+        <v>24600</v>
+      </c>
+      <c r="I15" s="3">
         <v>24300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>25000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>22500</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L15" s="3" t="s">
         <v>8</v>
@@ -1523,8 +1546,8 @@
       <c r="M15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N15" s="3">
-        <v>0</v>
+      <c r="N15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O15" s="3">
         <v>0</v>
@@ -1595,8 +1618,11 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1631,222 +1657,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>768200</v>
+        <v>741300</v>
       </c>
       <c r="E17" s="3">
+        <v>765100</v>
+      </c>
+      <c r="F17" s="3">
         <v>783900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>786500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>746100</v>
       </c>
-      <c r="H17" s="3">
-        <v>720900</v>
-      </c>
       <c r="I17" s="3">
+        <v>720700</v>
+      </c>
+      <c r="J17" s="3">
         <v>738000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>753400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>712000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>728000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>760700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>742200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>706800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>653400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>661100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>655600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>603000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>549400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>534900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>545200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>577500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>584000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>622600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>612800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>618600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>602700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>620900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>599100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>583100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>554100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>565800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>519700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>481200</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>476600</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>503700</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>131900</v>
+        <v>128700</v>
       </c>
       <c r="E18" s="3">
+        <v>135000</v>
+      </c>
+      <c r="F18" s="3">
         <v>151500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>141400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>130600</v>
       </c>
-      <c r="H18" s="3">
-        <v>125400</v>
-      </c>
       <c r="I18" s="3">
+        <v>125600</v>
+      </c>
+      <c r="J18" s="3">
         <v>141500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>122300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>116300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>119300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>129300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>111000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>95700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>107500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>112000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>109400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>76100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>87200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>82500</v>
-      </c>
-      <c r="V18" s="3">
-        <v>84500</v>
       </c>
       <c r="W18" s="3">
         <v>84500</v>
       </c>
       <c r="X18" s="3">
+        <v>84500</v>
+      </c>
+      <c r="Y18" s="3">
         <v>88700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>104400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>100000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>85100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>98700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>103800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>100900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>81600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>90700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>94300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>88500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>69400</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>76400</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>90100</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1884,317 +1917,324 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-5200</v>
+        <v>-4400</v>
       </c>
       <c r="E20" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="F20" s="3">
         <v>400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-7600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-4000</v>
       </c>
-      <c r="H20" s="3">
-        <v>-3000</v>
-      </c>
       <c r="I20" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="J20" s="3">
         <v>-2500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-4300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>3400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>4100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>2400</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>5100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>4700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>2700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>4300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>2800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>2600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>4700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>1900</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>5300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>3500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-800</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>2500</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>600</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>1700</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>8100</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-2700</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>162600</v>
+        <v>158100</v>
       </c>
       <c r="E21" s="3">
+        <v>164800</v>
+      </c>
+      <c r="F21" s="3">
         <v>176000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>173600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>159200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>152700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>169000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>149100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>140300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>143500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>155500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>138600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>121800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>131300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>142000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>137900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>100500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>109000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>108200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>110600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>108900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>112500</v>
-      </c>
-      <c r="Y21" s="3">
-        <v>125300</v>
       </c>
       <c r="Z21" s="3">
         <v>125300</v>
       </c>
       <c r="AA21" s="3">
+        <v>125300</v>
+      </c>
+      <c r="AB21" s="3">
         <v>105700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>119900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>128400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>123900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>100500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>108800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>116200</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>107600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>89500</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>103400</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>106400</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E22" s="3">
         <v>5500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>5300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>5000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>5600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>5500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>4900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>5100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>4600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>4500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>4100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>3800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>3600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>3400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>3100</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>3200</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>3300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>3500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>3900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>4400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>4500</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>4700</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>5200</v>
       </c>
       <c r="Z22" s="3">
         <v>5200</v>
       </c>
       <c r="AA22" s="3">
+        <v>5200</v>
+      </c>
+      <c r="AB22" s="3">
         <v>5300</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>4200</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>5600</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>5400</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>5100</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>5200</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>5100</v>
-      </c>
-      <c r="AH22" s="3">
-        <v>4800</v>
       </c>
       <c r="AI22" s="3">
         <v>4800</v>
@@ -2203,224 +2243,233 @@
         <v>4800</v>
       </c>
       <c r="AK22" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AL22" s="3">
         <v>4900</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>125000</v>
+      </c>
+      <c r="E23" s="3">
         <v>130500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>139400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>144000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>129000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>122900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>117300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>121500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>113300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>116600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>128600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>111300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>94500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>104100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>114000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>110900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>73900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>82200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>81300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>84400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>82800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>86600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>98800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>99500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>80500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>96400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>103500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>99000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>76400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>84700</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>91700</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>84300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>66300</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>79700</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>82500</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>29100</v>
+      </c>
+      <c r="E24" s="3">
         <v>31500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>29700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>30500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>30300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>30800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>25400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>27800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>27300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>29400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>27600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>28300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>22700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>27000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>29700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>26500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>17700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>20300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>17200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>21000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>18400</v>
-      </c>
-      <c r="X24" s="3">
-        <v>21600</v>
       </c>
       <c r="Y24" s="3">
         <v>21600</v>
       </c>
       <c r="Z24" s="3">
+        <v>21600</v>
+      </c>
+      <c r="AA24" s="3">
         <v>24300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>20000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>23500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>27100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>28700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>119000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>23800</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>23500</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>24200</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>19800</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>21700</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>23000</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2526,222 +2575,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>95900</v>
+      </c>
+      <c r="E26" s="3">
         <v>99000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>109700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>113500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>98700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>92100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>91900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>93700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>86000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>87200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>101000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>83000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>71800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>77100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>84300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>84400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>56200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>61900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>64100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>63400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>64400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>65000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>77200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>75200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>60500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>72900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>76400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>70300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-42600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>60900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>68200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>60100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>46500</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>58000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>59500</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>95900</v>
+      </c>
+      <c r="E27" s="3">
         <v>99000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>109700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>113500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>98700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>92100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>91900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>93700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>86000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>87200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>101000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>83000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>71800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>77100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>84300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>84400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>56200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>61900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>64100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>63400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>64400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>65000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>77200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>75200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>60500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>72900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>76400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>70300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-42600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>60900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>68200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>60100</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>46500</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>58000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>59500</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2847,8 +2905,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2894,8 +2955,8 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>8</v>
+      <c r="R29" s="3">
+        <v>0</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>8</v>
@@ -2915,29 +2976,29 @@
       <c r="X29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Y29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z29" s="3">
         <v>-19100</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
-      </c>
       <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3">
         <v>-400</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>900</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>26000</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>-400</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>-10300</v>
-      </c>
-      <c r="AF29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>8</v>
@@ -2954,8 +3015,11 @@
       <c r="AK29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3061,8 +3125,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3168,222 +3235,231 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>5200</v>
+        <v>4400</v>
       </c>
       <c r="E32" s="3">
+        <v>4300</v>
+      </c>
+      <c r="F32" s="3">
         <v>-400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>7600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>4000</v>
       </c>
-      <c r="H32" s="3">
-        <v>3000</v>
-      </c>
       <c r="I32" s="3">
+        <v>2800</v>
+      </c>
+      <c r="J32" s="3">
         <v>2500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>4300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-3400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-4100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-2400</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-5100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-4700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-2700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-4300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-2800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-2600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-4700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-5300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-3500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>800</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-2500</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-600</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-1700</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-8100</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>95900</v>
+      </c>
+      <c r="E33" s="3">
         <v>99000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>109700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>113500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>98700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>92100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>91900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>93700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>86000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>87200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>101000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>83000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>71800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>77100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>84300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>84400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>56200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>61900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>64100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>63400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>64400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>65000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>58100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>75200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>60100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>73800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>102400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>69900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-52900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>60900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>68200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>60100</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>46500</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>58000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>59500</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3489,227 +3565,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>95900</v>
+      </c>
+      <c r="E35" s="3">
         <v>99000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>109700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>113500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>98700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>92100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>91900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>93700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>86000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>87200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>101000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>83000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>71800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>77100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>84300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>84400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>56200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>61900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>64100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>63400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>64400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>65000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>58100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>75200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>60100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>73800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>102400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>69900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-52900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>60900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>68200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>60100</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>46500</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>58000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>59500</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E38" s="2">
         <v>45596</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45504</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45412</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45322</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45230</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45138</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45046</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44957</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44865</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44773</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44681</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44592</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44500</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44408</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44316</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44227</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44135</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44043</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43951</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43861</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43769</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43677</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43585</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43496</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43404</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43312</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43220</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43131</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43039</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42947</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42855</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42766</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42674</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42582</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3747,8 +3832,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3786,115 +3872,119 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>189100</v>
+      </c>
+      <c r="E41" s="3">
         <v>221200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>232700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>223700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>193800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>217800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>187100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>186000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>179400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>161000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>193300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>168700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>170400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>200800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>222800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>215300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>207300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>270000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>236600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>326500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>211100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>210000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>177800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>203800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>191200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>199900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>204700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>317300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>362200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>349600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>308400</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>295900</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>296300</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>262200</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>243200</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4000,492 +4090,507 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>631300</v>
+        <v>614200</v>
       </c>
       <c r="E43" s="3">
+        <v>650100</v>
+      </c>
+      <c r="F43" s="3">
         <v>645600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>653200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>610500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>594400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>613000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>641700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>592200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>601100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>634300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>604200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>570900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>563400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>567600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>553800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>504300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>476900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>455300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>460500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>475800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>501500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>529500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>534300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>515300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>542400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>534600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>530600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>509900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>483000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>497700</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>459200</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>408400</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>415000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>452400</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>540800</v>
+      </c>
+      <c r="E44" s="3">
         <v>520000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>476700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>444700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>433400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>429600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>418100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>449700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>501300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>490100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>502400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>510700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>480700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>444700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>384500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>360100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>347600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>329500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>322700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>346500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>350100</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>361500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>332800</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>359500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>365600</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>360500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>334100</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>344200</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>344900</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>319600</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>293500</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>272800</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>260400</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>249200</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>234100</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
+      <c r="D45" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E45" s="3">
+        <v>2800</v>
+      </c>
+      <c r="F45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E45" s="3" t="s">
+      <c r="G45" s="3">
+        <v>1100</v>
+      </c>
+      <c r="H45" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I45" s="3">
+        <v>2300</v>
+      </c>
+      <c r="J45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F45" s="3">
-        <v>1100</v>
-      </c>
-      <c r="G45" s="3">
-        <v>1200</v>
-      </c>
-      <c r="H45" s="3">
-        <v>2300</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>76200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>83200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>76500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>83700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>92200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>86900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>69100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>69500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>67100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>67200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>82100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>87000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>84200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>86100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>82500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>76000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>85600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>67600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>52300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>57100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>62900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>52100</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>51400</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>56100</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>60100</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>66600</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>80000</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1422500</v>
+      </c>
+      <c r="E46" s="3">
         <v>1479400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1438100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1400700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1317200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1313100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1286000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1352600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1349100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1335400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1406500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1367300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1314200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1295800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1244000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1198700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1126300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1143600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1096700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1220500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1121200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1159100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1122600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1173600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1157700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1170400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1125700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1249200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1279900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1204300</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1151000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>1084000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>1025200</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>993000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>1009700</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>8</v>
+      <c r="D47" s="3">
+        <v>97700</v>
       </c>
       <c r="E47" s="3">
+        <v>102700</v>
+      </c>
+      <c r="F47" s="3">
         <v>26900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>25900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>24300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>23500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>24400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>24300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>20500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>20400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>22400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>25600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>23700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>23900</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>24200</v>
       </c>
       <c r="R47" s="3">
         <v>24200</v>
       </c>
       <c r="S47" s="3">
+        <v>24200</v>
+      </c>
+      <c r="T47" s="3">
         <v>23300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>22300</v>
-      </c>
-      <c r="U47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="V47" s="3" t="s">
         <v>8</v>
@@ -4496,8 +4601,8 @@
       <c r="X47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y47" s="3">
-        <v>0</v>
+      <c r="Y47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z47" s="3">
         <v>0</v>
@@ -4535,222 +4640,231 @@
       <c r="AK47" s="3">
         <v>0</v>
       </c>
+      <c r="AL47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>637800</v>
+      </c>
+      <c r="E48" s="3">
         <v>647400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>705200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>642800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>647000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>642300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>712300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>640900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>625800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>590800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>594400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>591100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>601000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>609700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>617800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>626300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>624300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>617100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>705300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>685700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>699100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>685500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>588900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>569800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>552500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>517900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>509300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>511100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>507700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>483800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>484600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>462500</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>459700</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>466100</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>2771000</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>630100</v>
+      </c>
+      <c r="E49" s="3">
         <v>648200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>650300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>649900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>655300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>651000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>669200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>519100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>446600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>435300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>445600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>410400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>423700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>379800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>384100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>386500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>387400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>379800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>384100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>369100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>378200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>379100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>374000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>383700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>388000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>386700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>274000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>277100</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>280200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>277400</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>278700</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>268100</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>268800</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>270500</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>306300</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4856,8 +4970,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4963,115 +5080,121 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>268600</v>
+        <v>173200</v>
       </c>
       <c r="E52" s="3">
+        <v>165900</v>
+      </c>
+      <c r="F52" s="3">
         <v>93800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>146800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>139700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>138700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>78600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>138600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>136600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>130100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>131400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>124800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>128700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>129300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>130100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>118900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>109800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>106600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>58500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>63200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>63700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>59600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>57100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>78800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>68100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>69000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>67600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>57600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>63500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>66900</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>65400</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>65700</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>64000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>64500</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>39700</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5177,115 +5300,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2961300</v>
+      </c>
+      <c r="E54" s="3">
         <v>3043600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2914300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2866100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2783500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2768600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2770500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2675500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2578600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2512000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2600300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2519200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2491300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2438500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2400200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2354600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2271100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2269400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2244600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2338500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2262200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2283300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2142600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2205900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>2166300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>2144000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>1976600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>2095000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>2131300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>2032400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>1979700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1880300</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1817700</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>1794100</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>1787000</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5323,8 +5452,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5362,650 +5492,669 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>375200</v>
+      </c>
+      <c r="E57" s="3">
         <v>373500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>379400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>370000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>325800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>324900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>304900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>311100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>302100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>320700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>338500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>335800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>324500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>310000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>293900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>268100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>228100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>209400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>187700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>202700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>210100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>229100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>237500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>238700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>226700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>230600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>201300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>201500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>200000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>190600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>194000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>179000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>157800</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>160700</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>143300</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>62700</v>
+      </c>
+      <c r="E58" s="3">
         <v>103200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>73500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>74400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>262100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>284800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>176900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>151600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>3700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>31300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>63900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>41200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>48500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>44500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>22400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>6700</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>9500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>58100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>84700</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>110900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>52300</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>50600</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>66000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>74000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>43500</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>4500</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>18100</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>39200</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>73900</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>306900</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>277100</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>245000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>216700</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>215600</v>
+      </c>
+      <c r="E59" s="3">
         <v>188600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>187200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>167600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>195300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>162700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>153500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>143500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>274000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>248400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>287400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>239400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>250100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>230700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>264200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>236200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>249000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>203300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>209600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>172000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>203400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>191100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>193100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>157100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>200400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>183000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>224600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>191700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>216900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>185300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>216200</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>169000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>180600</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>157700</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>183800</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>765800</v>
+      </c>
+      <c r="E60" s="3">
         <v>800600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>782500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>735200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>893500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>882600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>756400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>712000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>580100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>569300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>629600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>606500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>638500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>581900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>606600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>548800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>499500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>419400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>406800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>432800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>498200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>531100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>482900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>446400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>493100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>487600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>469400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>397700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>435000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>415100</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>484100</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>654900</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>615500</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>563400</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>543800</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>514700</v>
+      </c>
+      <c r="E61" s="3">
         <v>538600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>524700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>481800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>352000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>366600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>539000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>470500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>624800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>600700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>644300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>607200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>553900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>548100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>461000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>454600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>495100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>576300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>617400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>735100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>595800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>596800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>584400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>644400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>632500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>630600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>499600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>687500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>667700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>631700</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>537300</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>298100</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>297800</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>324700</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>350200</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>123100</v>
+      </c>
+      <c r="E62" s="3">
         <v>146100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>77200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>147600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>140300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>155900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>104000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>161600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>179500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>187200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>193200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>181900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>182100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>192600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>195500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>197800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>202100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>210200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>216600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>215800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>217000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>227700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>172600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>157300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>155000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>158500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>149800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>173400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>201700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>104600</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>103800</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>125300</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>123700</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>121300</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>121600</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6111,8 +6260,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6218,8 +6370,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6325,115 +6480,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1416900</v>
+      </c>
+      <c r="E66" s="3">
         <v>1500600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1425200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1382100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1407700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1432500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1449800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1376800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1384400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1357200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1467100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1395600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1374500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1322600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1263100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1201200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1196700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1222600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1257500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1399700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1327400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1371700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1255300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1266200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1298900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1294400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1123600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1263300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1309000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1156100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1129600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1082600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1041200</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>1013500</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>1019600</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6471,8 +6632,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6578,8 +6740,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6685,8 +6850,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6792,8 +6960,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6899,115 +7070,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>8</v>
+      <c r="D72" s="3">
+        <v>2507800</v>
       </c>
       <c r="E72" s="3">
+        <v>2476400</v>
+      </c>
+      <c r="F72" s="3">
         <v>2377500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2332500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2219000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2180200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2087800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2056500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1962800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1932800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1849000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1802600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1718000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1700400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1621200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>1591200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>1507600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>1504900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>1445900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>1432800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>1368600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>1361100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1303200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1298300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1223800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1213800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1143400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1089100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1016400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>1120200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>1056900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>1035900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>977300</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>977500</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>921800</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7113,8 +7290,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7220,8 +7400,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7327,115 +7510,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1544400</v>
+      </c>
+      <c r="E76" s="3">
         <v>1543000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1489100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1484000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1375800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1336100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1320700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1298700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1194200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1154800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1133200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1123600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1116800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1115900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1137100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1153400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1074400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1046800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>987100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>938800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>934800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>911600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>887300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>939700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>867400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>849600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>853000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>831700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>822300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>876300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>850100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>797700</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>776500</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>780600</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>767400</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7541,227 +7730,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45688</v>
+      </c>
+      <c r="E80" s="2">
         <v>45596</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45504</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45412</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45322</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45230</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45138</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45046</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44957</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44865</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44773</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44681</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44592</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44500</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44408</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44316</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44227</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44135</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44043</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43951</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43861</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43769</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43677</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43585</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43496</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43404</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43312</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43220</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43131</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43039</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42947</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42855</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42766</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42674</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42582</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>95900</v>
+      </c>
+      <c r="E81" s="3">
         <v>99000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>109700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>113500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>98700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>92100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>91900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>93700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>86000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>87200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>101000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>83000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>71800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>77100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>84300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>84400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>56200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>61900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>64100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>63400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>64400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>65000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>58100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>75200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>60100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>73800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>102400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>69900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-52900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>60900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>68200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>60100</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>46500</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>58000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>59500</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7799,115 +7997,119 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>20800</v>
+      </c>
+      <c r="E83" s="3">
         <v>20300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>21600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>19600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>19800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>19900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>20500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>21100</v>
-      </c>
-      <c r="K83" s="3">
-        <v>22400</v>
       </c>
       <c r="L83" s="3">
         <v>22400</v>
       </c>
       <c r="M83" s="3">
+        <v>22400</v>
+      </c>
+      <c r="N83" s="3">
         <v>22800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>23500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>23700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>23800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>24900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>23800</v>
-      </c>
-      <c r="S83" s="3">
-        <v>23300</v>
       </c>
       <c r="T83" s="3">
         <v>23300</v>
       </c>
       <c r="U83" s="3">
+        <v>23300</v>
+      </c>
+      <c r="V83" s="3">
         <v>23000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>21800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>21600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>21200</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>21300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>20600</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>19900</v>
-      </c>
-      <c r="AB83" s="3">
-        <v>19300</v>
       </c>
       <c r="AC83" s="3">
         <v>19300</v>
       </c>
       <c r="AD83" s="3">
+        <v>19300</v>
+      </c>
+      <c r="AE83" s="3">
         <v>19500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>19000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>18900</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>19400</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>18500</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>18400</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>18900</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8013,8 +8215,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8120,8 +8325,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8227,8 +8435,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8334,8 +8545,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8441,115 +8655,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>90400</v>
+      </c>
+      <c r="E89" s="3">
         <v>72900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>126000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>141500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>87000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>138000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>190800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>133200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>102300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>118200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>108900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>64100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>36900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>42900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>96300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>103300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>73400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>128900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>121800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>88400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>90700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>86100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>122600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>80400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>79500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>63300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>104200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>48900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>45900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>63900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>87000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>61300</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>69800</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>99700</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>84200</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8587,115 +8807,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-18900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-25000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-19800</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-21300</v>
       </c>
       <c r="G91" s="3">
         <v>-21300</v>
       </c>
       <c r="H91" s="3">
+        <v>-21300</v>
+      </c>
+      <c r="I91" s="3">
         <v>-23200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-25700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-35200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-29500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-28100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-28700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-23300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-15200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-18300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-18800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-9800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-11600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-18800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-18200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-26500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-42600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-37100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-38300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-45300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-38900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-28200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-24400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-27300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-25900</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-19900</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-24700</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-32400</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-37600</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-12400</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-13500</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8801,8 +9025,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8908,115 +9135,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-19100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-96000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-19100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-23300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-21300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-23200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-172200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-97500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-29500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-28100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-48200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-23300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-64200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-18300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-18100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-9800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-11600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-18800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-22700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-26500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-42600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-37100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-38000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-45300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-38900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-124200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-23100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-27300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-25900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-19100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-43600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-16200</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-12600</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-23300</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-11300</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9054,61 +9287,62 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>32200</v>
+      </c>
+      <c r="E96" s="3">
         <v>32400</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>32500</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>30000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>30100</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>30200</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>30300</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>27900</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-28000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-28200</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-28300</v>
-      </c>
-      <c r="N96" s="3">
-        <v>-27200</v>
       </c>
       <c r="O96" s="3">
         <v>-27200</v>
       </c>
       <c r="P96" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-27400</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-27700</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-26400</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-26500</v>
-      </c>
-      <c r="T96" s="3">
-        <v>-26600</v>
       </c>
       <c r="U96" s="3">
         <v>-26600</v>
@@ -9123,22 +9357,22 @@
         <v>-26600</v>
       </c>
       <c r="Y96" s="3">
+        <v>-26600</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-26800</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-24200</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-24300</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-24400</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-24500</v>
-      </c>
-      <c r="AD96" s="3">
-        <v>-23400</v>
       </c>
       <c r="AE96" s="3">
         <v>-23400</v>
@@ -9147,22 +9381,25 @@
         <v>-23400</v>
       </c>
       <c r="AG96" s="3">
+        <v>-23400</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-22900</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-23200</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-23100</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-23200</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-23300</v>
       </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9268,8 +9505,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9375,8 +9615,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9482,325 +9725,337 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-98300</v>
+      </c>
+      <c r="E100" s="3">
         <v>9800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-98400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-85800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-92800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-78900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-18100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-27300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-64000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-112800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-31400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-37100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-45500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-67800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-84900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-131700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-78900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-195800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>59300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-48300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-14700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-109600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-19700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-55300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>61300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-184700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-61500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-20700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-1900</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-40000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-46200</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-16300</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-55200</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-73500</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-5200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-1800</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>9600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-9600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-4700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-5400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>9600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-9600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-4700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-5400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-2900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-2900</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-600</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>7200</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>2200</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>6800</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-5800</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>1300</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-2100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-1000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-2800</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>6000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-5200</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-9000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-5000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>13300</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-1700</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>9900</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>2200</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-1600</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-2200</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-3600</v>
       </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-32100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-11500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>9000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>29900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-24000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>30700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>6600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>18400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-32300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>24600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-30400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-22000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>7500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>8000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-62700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>33400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-89900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>115400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>1100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>32200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-26000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>12600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-8700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-4800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-112600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-44900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>12600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>41200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>12500</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-400</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>34100</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>19000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-4200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DCI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DCI_QTR_FIN.xlsx
@@ -656,493 +656,505 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45777</v>
+      </c>
+      <c r="E7" s="2">
         <v>45688</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45596</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45504</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45412</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45322</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45230</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45138</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45046</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44957</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44865</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44773</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44681</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44592</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44500</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44408</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44316</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44227</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44135</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44043</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43951</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43861</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43769</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43677</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43585</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43496</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43404</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43312</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43220</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43131</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43039</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42947</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42855</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42766</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42674</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42582</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>940100</v>
+      </c>
+      <c r="E8" s="3">
         <v>870000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>900100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>935400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>927900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>876700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>846300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>879500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>875700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>828300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>847300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>890000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>853200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>802500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>760900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>773100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>765000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>679100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>636600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>617400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>629700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>662000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>672700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>727000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>712800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>703700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>701400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>724700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>700000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>664700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>644800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>660100</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>608200</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>550600</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>553000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>593800</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>615600</v>
+      </c>
+      <c r="E9" s="3">
         <v>563500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>579400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>596800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>597800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>568100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>545400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>576500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>586900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>543900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>560100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>598400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>584200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>552700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>501400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>507400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>507000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>448000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>413900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>409500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>420500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>438800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>441400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>483200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>472100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>478300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>463000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>471700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>460400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>445800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>420500</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>430600</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>396700</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>362700</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>358800</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>384500</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>324500</v>
+      </c>
+      <c r="E10" s="3">
         <v>306500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>320700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>338600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>330100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>308600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>300900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>303000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>288800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>284400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>287200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>291600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>269000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>249800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>259500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>265700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>258000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>231100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>222700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>207900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>209200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>223200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>231300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>243800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>240700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>225400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>238400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>253000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>239600</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>218900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>224300</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>229500</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>211500</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>187900</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>194200</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>209300</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1181,43 +1193,44 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>21400</v>
+      </c>
+      <c r="E12" s="3">
         <v>21200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>22700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>25400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>24800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>22100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>21300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>21900</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>19000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>18500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>18700</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O12" s="3" t="s">
         <v>8</v>
@@ -1291,8 +1304,11 @@
       <c r="AL12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1401,22 +1417,25 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>2200</v>
+        <v>60000</v>
       </c>
       <c r="E14" s="3">
+        <v>6600</v>
+      </c>
+      <c r="F14" s="3">
         <v>3300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>6400</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>8</v>
@@ -1424,11 +1443,11 @@
       <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K14" s="3">
         <v>21800</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>8</v>
@@ -1445,20 +1464,20 @@
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="3">
         <v>2500</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
-      <c r="S14" s="3" t="s">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>14800</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>8</v>
@@ -1472,8 +1491,8 @@
       <c r="Y14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
@@ -1511,37 +1530,40 @@
       <c r="AL14" s="3">
         <v>0</v>
       </c>
+      <c r="AM14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>24600</v>
+      </c>
+      <c r="E15" s="3">
         <v>25000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>25500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>24900</v>
-      </c>
-      <c r="G15" s="3">
-        <v>24600</v>
       </c>
       <c r="H15" s="3">
         <v>24600</v>
       </c>
       <c r="I15" s="3">
+        <v>24600</v>
+      </c>
+      <c r="J15" s="3">
         <v>24300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>25000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>22500</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M15" s="3" t="s">
         <v>8</v>
@@ -1549,8 +1571,8 @@
       <c r="N15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
+      <c r="O15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P15" s="3">
         <v>0</v>
@@ -1621,8 +1643,11 @@
       <c r="AL15" s="3">
         <v>0</v>
       </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1658,228 +1683,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>741300</v>
+        <v>791800</v>
       </c>
       <c r="E17" s="3">
+        <v>736900</v>
+      </c>
+      <c r="F17" s="3">
         <v>765100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>783900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>786500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>746100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>720700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>738000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>753400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>712000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>728000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>760700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>742200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>706800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>653400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>661100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>655600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>603000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>549400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>534900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>545200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>577500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>584000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>622600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>612800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>618600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>602700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>620900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>599100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>583100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>554100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>565800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>519700</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>481200</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>476600</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>503700</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>128700</v>
+        <v>148300</v>
       </c>
       <c r="E18" s="3">
+        <v>133100</v>
+      </c>
+      <c r="F18" s="3">
         <v>135000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>151500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>141400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>130600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>125600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>141500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>122300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>116300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>119300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>129300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>111000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>95700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>107500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>112000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>109400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>76100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>87200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>82500</v>
-      </c>
-      <c r="W18" s="3">
-        <v>84500</v>
       </c>
       <c r="X18" s="3">
         <v>84500</v>
       </c>
       <c r="Y18" s="3">
+        <v>84500</v>
+      </c>
+      <c r="Z18" s="3">
         <v>88700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>104400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>100000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>85100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>98700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>103800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>100900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>81600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>90700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>94300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>88500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>69400</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>76400</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>90100</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1918,8 +1950,9 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1927,317 +1960,323 @@
         <v>-4400</v>
       </c>
       <c r="E20" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="F20" s="3">
         <v>-4300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-7600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-4000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-2800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-2500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-4300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>3400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>4100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>2400</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>5100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>4700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>2700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>4300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>2800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>2600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>4700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>1900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>5300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>3500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-100</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-800</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>2500</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>600</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>1700</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>8100</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-2700</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>158100</v>
+        <v>177300</v>
       </c>
       <c r="E21" s="3">
+        <v>162500</v>
+      </c>
+      <c r="F21" s="3">
         <v>164800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>176000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>173600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>159200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>152700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>169000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>149100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>140300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>143500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>155500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>138600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>121800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>131300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>142000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>137900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>100500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>109000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>108200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>110600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>108900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>112500</v>
-      </c>
-      <c r="Z21" s="3">
-        <v>125300</v>
       </c>
       <c r="AA21" s="3">
         <v>125300</v>
       </c>
       <c r="AB21" s="3">
+        <v>125300</v>
+      </c>
+      <c r="AC21" s="3">
         <v>105700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>119900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>128400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>123900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>100500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>108800</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>116200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>107600</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>89500</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>103400</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>106400</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E22" s="3">
         <v>5900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>5500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>5300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>5000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>5600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>5500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>4900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>5100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>4600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>4500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>4100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>3800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>3600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>3400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>3100</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>3200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>3300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>3500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>3900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>4400</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>4500</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>4700</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>5200</v>
       </c>
       <c r="AA22" s="3">
         <v>5200</v>
       </c>
       <c r="AB22" s="3">
+        <v>5200</v>
+      </c>
+      <c r="AC22" s="3">
         <v>5300</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>4200</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>5600</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>5400</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>5100</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>5200</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>5100</v>
-      </c>
-      <c r="AI22" s="3">
-        <v>4800</v>
       </c>
       <c r="AJ22" s="3">
         <v>4800</v>
@@ -2246,230 +2285,239 @@
         <v>4800</v>
       </c>
       <c r="AL22" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AM22" s="3">
         <v>4900</v>
       </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>87000</v>
+      </c>
+      <c r="E23" s="3">
         <v>125000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>130500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>139400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>144000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>129000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>122900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>117300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>121500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>113300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>116600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>128600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>111300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>94500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>104100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>114000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>110900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>73900</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>82200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>81300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>84400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>82800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>86600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>98800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>99500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>80500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>96400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>103500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>99000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>76400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>84700</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>91700</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>84300</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>66300</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>79700</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>82500</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>29200</v>
+      </c>
+      <c r="E24" s="3">
         <v>29100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>31500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>29700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>30500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>30300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>30800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>25400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>27800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>27300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>29400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>27600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>28300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>22700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>27000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>29700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>26500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>17700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>20300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>17200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>21000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>18400</v>
-      </c>
-      <c r="Y24" s="3">
-        <v>21600</v>
       </c>
       <c r="Z24" s="3">
         <v>21600</v>
       </c>
       <c r="AA24" s="3">
+        <v>21600</v>
+      </c>
+      <c r="AB24" s="3">
         <v>24300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>20000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>23500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>27100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>28700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>119000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>23800</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>23500</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>24200</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>19800</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>21700</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>23000</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2578,228 +2626,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>57800</v>
+      </c>
+      <c r="E26" s="3">
         <v>95900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>99000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>109700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>113500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>98700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>92100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>91900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>93700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>86000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>87200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>101000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>83000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>71800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>77100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>84300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>84400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>56200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>61900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>64100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>63400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>64400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>65000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>77200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>75200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>60500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>72900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>76400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>70300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-42600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>60900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>68200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>60100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>46500</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>58000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>59500</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>57800</v>
+      </c>
+      <c r="E27" s="3">
         <v>95900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>99000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>109700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>113500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>98700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>92100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>91900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>93700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>86000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>87200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>101000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>83000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>71800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>77100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>84300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>84400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>56200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>61900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>64100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>63400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>64400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>65000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>77200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>75200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>60500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>72900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>76400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>70300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-42600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>60900</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>68200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>60100</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>46500</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>58000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>59500</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2908,8 +2965,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2958,8 +3018,8 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>8</v>
+      <c r="S29" s="3">
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>8</v>
@@ -2979,29 +3039,29 @@
       <c r="Y29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="Z29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA29" s="3">
         <v>-19100</v>
       </c>
-      <c r="AA29" s="3">
-        <v>0</v>
-      </c>
       <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3">
         <v>-400</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>900</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>26000</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>-400</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>-10300</v>
-      </c>
-      <c r="AG29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AH29" s="3" t="s">
         <v>8</v>
@@ -3018,8 +3078,11 @@
       <c r="AL29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3128,8 +3191,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3238,8 +3304,11 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3247,219 +3316,225 @@
         <v>4400</v>
       </c>
       <c r="E32" s="3">
+        <v>4400</v>
+      </c>
+      <c r="F32" s="3">
         <v>4300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>7600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>4000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>2800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>2500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>4300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-3400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-4100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-5100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-4700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-2700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-4300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-2800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-2600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-4700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-1900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-5300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-3500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>100</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>800</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-2500</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-600</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-1700</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-8100</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>57800</v>
+      </c>
+      <c r="E33" s="3">
         <v>95900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>99000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>109700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>113500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>98700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>92100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>91900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>93700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>86000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>87200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>101000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>83000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>71800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>77100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>84300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>84400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>56200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>61900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>64100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>63400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>64400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>65000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>58100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>75200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>60100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>73800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>102400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>69900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-52900</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>60900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>68200</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>60100</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>46500</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>58000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>59500</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3568,233 +3643,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>57800</v>
+      </c>
+      <c r="E35" s="3">
         <v>95900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>99000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>109700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>113500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>98700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>92100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>91900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>93700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>86000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>87200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>101000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>83000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>71800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>77100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>84300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>84400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>56200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>61900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>64100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>63400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>64400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>65000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>58100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>75200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>60100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>73800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>102400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>69900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-52900</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>60900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>68200</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>60100</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>46500</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>58000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>59500</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45777</v>
+      </c>
+      <c r="E38" s="2">
         <v>45688</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45596</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45504</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45412</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45322</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45230</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45138</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45046</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44957</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44865</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44773</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44681</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44592</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44500</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44408</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44316</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44227</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44135</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44043</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43951</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43861</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43769</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43677</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43585</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43496</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43404</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43312</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43220</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43131</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43039</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42947</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42855</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42766</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42674</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42582</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3833,8 +3917,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3873,118 +3958,122 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>178500</v>
+      </c>
+      <c r="E41" s="3">
         <v>189100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>221200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>232700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>223700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>193800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>217800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>187100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>186000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>179400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>161000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>193300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>168700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>170400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>200800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>222800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>215300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>207300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>270000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>236600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>326500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>211100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>210000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>177800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>203800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>191200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>199900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>204700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>317300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>362200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>349600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>308400</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>295900</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>296300</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>262200</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>243200</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4093,507 +4182,522 @@
       <c r="AL42" s="3">
         <v>0</v>
       </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>685800</v>
+      </c>
+      <c r="E43" s="3">
         <v>614200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>650100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>645600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>653200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>610500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>594400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>613000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>641700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>592200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>601100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>634300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>604200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>570900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>563400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>567600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>553800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>504300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>476900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>455300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>460500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>475800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>501500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>529500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>534300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>515300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>542400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>534600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>530600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>509900</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>483000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>497700</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>459200</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>408400</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>415000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>452400</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>529400</v>
+      </c>
+      <c r="E44" s="3">
         <v>540800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>520000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>476700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>444700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>433400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>429600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>418100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>449700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>501300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>490100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>502400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>510700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>480700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>444700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>384500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>360100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>347600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>329500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>322700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>346500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>350100</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>361500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>332800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>359500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>365600</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>360500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>334100</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>344200</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>344900</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>319600</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>293500</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>272800</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>260400</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>249200</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>234100</v>
       </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E45" s="3">
         <v>4100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2800</v>
       </c>
-      <c r="F45" s="3" t="s">
+      <c r="G45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2300</v>
       </c>
-      <c r="J45" s="3" t="s">
+      <c r="K45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>76200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>83200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>76500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>83700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>92200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>86900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>69100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>69500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>67100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>67200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>82100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>87000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>84200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>86100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>82500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>76000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>85600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>67600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>52300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>57100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>62900</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>52100</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>51400</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>56100</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>60100</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>66600</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>80000</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1475500</v>
+      </c>
+      <c r="E46" s="3">
         <v>1422500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1479400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1438100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1400700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1317200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1313100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1286000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1352600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1349100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1335400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1406500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1367300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1314200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1295800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1244000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1198700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1126300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1143600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1096700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1220500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1121200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1159100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1122600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1173600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1157700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1170400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1125700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1249200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1279900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1204300</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>1151000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>1084000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>1025200</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>993000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>1009700</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>102000</v>
+      </c>
+      <c r="E47" s="3">
         <v>97700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>102700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>26900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>25900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>24300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>23500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>24400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>24300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>20500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>20400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>22400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>25600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>23700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>23900</v>
-      </c>
-      <c r="R47" s="3">
-        <v>24200</v>
       </c>
       <c r="S47" s="3">
         <v>24200</v>
       </c>
       <c r="T47" s="3">
+        <v>24200</v>
+      </c>
+      <c r="U47" s="3">
         <v>23300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>22300</v>
-      </c>
-      <c r="V47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="W47" s="3" t="s">
         <v>8</v>
@@ -4604,8 +4708,8 @@
       <c r="Y47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z47" s="3">
-        <v>0</v>
+      <c r="Z47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA47" s="3">
         <v>0</v>
@@ -4643,228 +4747,237 @@
       <c r="AL47" s="3">
         <v>0</v>
       </c>
+      <c r="AM47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>648300</v>
+      </c>
+      <c r="E48" s="3">
         <v>637800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>647400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>705200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>642800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>647000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>642300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>712300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>640900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>625800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>590800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>594400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>591100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>601000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>609700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>617800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>626300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>624300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>617100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>705300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>685700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>699100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>685500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>588900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>569800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>552500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>517900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>509300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>511100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>507700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>483800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>484600</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>462500</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>459700</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>466100</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>2771000</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>591500</v>
+      </c>
+      <c r="E49" s="3">
         <v>630100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>648200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>650300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>649900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>655300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>651000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>669200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>519100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>446600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>435300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>445600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>410400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>423700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>379800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>384100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>386500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>387400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>379800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>384100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>369100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>378200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>379100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>374000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>383700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>388000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>386700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>274000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>277100</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>280200</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>277400</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>278700</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>268100</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>268800</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>270500</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>306300</v>
       </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4973,8 +5086,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5083,118 +5199,124 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>179200</v>
+      </c>
+      <c r="E52" s="3">
         <v>173200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>165900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>93800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>146800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>139700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>138700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>78600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>138600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>136600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>130100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>131400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>124800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>128700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>129300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>130100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>118900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>109800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>106600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>58500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>63200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>63700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>59600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>57100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>78800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>68100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>69000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>67600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>57600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>63500</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>66900</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>65400</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>65700</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>64000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>64500</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>39700</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5303,118 +5425,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2996500</v>
+      </c>
+      <c r="E54" s="3">
         <v>2961300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3043600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2914300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2866100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2783500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2768600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2770500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2675500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2578600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2512000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2600300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2519200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2491300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2438500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2400200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2354600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2271100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2269400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2244600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2338500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2262200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>2283300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2142600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>2205900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>2166300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>2144000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>1976600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>2095000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>2131300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>2032400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>1979700</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1880300</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>1817700</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>1794100</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>1787000</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5453,8 +5581,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5493,668 +5622,687 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>362000</v>
+      </c>
+      <c r="E57" s="3">
         <v>375200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>373500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>379400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>370000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>325800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>324900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>304900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>311100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>302100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>320700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>338500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>335800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>324500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>310000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>293900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>268100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>228100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>209400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>187700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>202700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>210100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>229100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>237500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>238700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>226700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>230600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>201300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>201500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>200000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>190600</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>194000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>179000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>157800</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>160700</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>143300</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>83600</v>
+      </c>
+      <c r="E58" s="3">
         <v>62700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>103200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>73500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>74400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>262100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>284800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>176900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>151600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>4000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>3700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>31300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>63900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>41200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>48500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>44500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>22400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>6700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>9500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>58100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>84700</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>110900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>52300</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>50600</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>66000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>74000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>43500</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>4500</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>18100</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>39200</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>73900</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>306900</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>277100</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>245000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>216700</v>
       </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>179700</v>
+      </c>
+      <c r="E59" s="3">
         <v>215600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>188600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>187200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>167600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>195300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>162700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>153500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>143500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>274000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>248400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>287400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>239400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>250100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>230700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>264200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>236200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>249000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>203300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>209600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>172000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>203400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>191100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>193100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>157100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>200400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>183000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>224600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>191700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>216900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>185300</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>216200</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>169000</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>180600</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>157700</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>183800</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>760100</v>
+      </c>
+      <c r="E60" s="3">
         <v>765800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>800600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>782500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>735200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>893500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>882600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>756400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>712000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>580100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>569300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>629600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>606500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>638500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>581900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>606600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>548800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>499500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>419400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>406800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>432800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>498200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>531100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>482900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>446400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>493100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>487600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>469400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>397700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>435000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>415100</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>484100</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>654900</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>615500</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>563400</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>543800</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>638800</v>
+      </c>
+      <c r="E61" s="3">
         <v>514700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>538600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>524700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>481800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>352000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>366600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>539000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>470500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>624800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>600700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>644300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>607200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>553900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>548100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>461000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>454600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>495100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>576300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>617400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>735100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>595800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>596800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>584400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>644400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>632500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>630600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>499600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>687500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>667700</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>631700</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>537300</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>298100</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>297800</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>324700</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>350200</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>122300</v>
+      </c>
+      <c r="E62" s="3">
         <v>123100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>146100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>77200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>147600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>140300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>155900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>104000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>161600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>179500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>187200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>193200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>181900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>182100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>192600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>195500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>197800</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>202100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>210200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>216600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>215800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>217000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>227700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>172600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>157300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>155000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>158500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>149800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>173400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>201700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>104600</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>103800</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>125300</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>123700</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>121300</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>121600</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6263,8 +6411,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6373,8 +6524,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6483,118 +6637,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1532300</v>
+      </c>
+      <c r="E66" s="3">
         <v>1416900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1500600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1425200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1382100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1407700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1432500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1449800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1376800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1384400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1357200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1467100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1395600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1374500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1322600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1263100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1201200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1196700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1222600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1257500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1399700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1327400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1371700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1255300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1266200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1298900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1294400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1123600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1263300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1309000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1156100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1129600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1082600</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>1041200</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>1013500</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>1019600</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6633,8 +6793,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6743,8 +6904,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6853,8 +7017,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6963,8 +7130,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7073,118 +7243,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2565600</v>
+      </c>
+      <c r="E72" s="3">
         <v>2507800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2476400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2377500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2332500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2219000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2180200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2087800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2056500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1962800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1932800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1849000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1802600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1718000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1700400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>1621200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>1591200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>1507600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>1504900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>1445900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>1432800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>1368600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1361100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1303200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1298300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1223800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1213800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1143400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1089100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>1016400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>1120200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>1056900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>1035900</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>977300</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>977500</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>921800</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7293,8 +7469,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7403,8 +7582,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7513,118 +7695,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1464200</v>
+      </c>
+      <c r="E76" s="3">
         <v>1544400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1543000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1489100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1484000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1375800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1336100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1320700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1298700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1194200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1154800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1133200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1123600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1116800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>1115900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>1137100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>1153400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>1074400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>1046800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>987100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>938800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>934800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>911600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>887300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>939700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>867400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>849600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>853000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>831700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>822300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>876300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>850100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>797700</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>776500</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>780600</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>767400</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7733,233 +7921,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45777</v>
+      </c>
+      <c r="E80" s="2">
         <v>45688</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45596</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45504</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45412</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45322</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45230</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45138</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45046</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44957</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44865</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44773</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44681</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44592</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44500</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44408</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44316</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44227</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44135</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44043</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43951</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43861</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43769</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43677</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43585</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43496</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43404</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43312</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43220</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43131</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43039</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42947</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42855</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42766</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42674</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42582</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>57800</v>
+      </c>
+      <c r="E81" s="3">
         <v>95900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>99000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>109700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>113500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>98700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>92100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>91900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>93700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>86000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>87200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>101000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>83000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>71800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>77100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>84300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>84400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>56200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>61900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>64100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>63400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>64400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>65000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>58100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>75200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>60100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>73800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>102400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>69900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-52900</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>60900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>68200</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>60100</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>46500</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>58000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>59500</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7998,118 +8195,122 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>20700</v>
+      </c>
+      <c r="E83" s="3">
         <v>20800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>20300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>21600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>19600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>19800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>19900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>20500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>21100</v>
-      </c>
-      <c r="L83" s="3">
-        <v>22400</v>
       </c>
       <c r="M83" s="3">
         <v>22400</v>
       </c>
       <c r="N83" s="3">
+        <v>22400</v>
+      </c>
+      <c r="O83" s="3">
         <v>22800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>23500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>23700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>23800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>24900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>23800</v>
-      </c>
-      <c r="T83" s="3">
-        <v>23300</v>
       </c>
       <c r="U83" s="3">
         <v>23300</v>
       </c>
       <c r="V83" s="3">
+        <v>23300</v>
+      </c>
+      <c r="W83" s="3">
         <v>23000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>21800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>21600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>21200</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>21300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>20600</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>19900</v>
-      </c>
-      <c r="AC83" s="3">
-        <v>19300</v>
       </c>
       <c r="AD83" s="3">
         <v>19300</v>
       </c>
       <c r="AE83" s="3">
+        <v>19300</v>
+      </c>
+      <c r="AF83" s="3">
         <v>19500</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>19000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>18900</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>19400</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>18500</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>18400</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>18900</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8218,8 +8419,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8328,8 +8532,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8438,8 +8645,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8548,8 +8758,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8658,118 +8871,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>87700</v>
+      </c>
+      <c r="E89" s="3">
         <v>90400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>72900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>126000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>141500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>87000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>138000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>190800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>133200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>102300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>118200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>108900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>64100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>36900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>42900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>96300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>103300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>73400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>128900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>121800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>88400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>90700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>86100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>122600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>80400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>79500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>63300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>104200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>48900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>45900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>63900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>87000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>61300</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>69800</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>99700</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>84200</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8808,118 +9027,122 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-14700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-18900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-25000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-19800</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-21300</v>
       </c>
       <c r="H91" s="3">
         <v>-21300</v>
       </c>
       <c r="I91" s="3">
+        <v>-21300</v>
+      </c>
+      <c r="J91" s="3">
         <v>-23200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-25700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-35200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-29500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-28100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-28700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-23300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-15200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-18300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-18800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-9800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-11600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-18800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-18200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-26500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-42600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-37100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-38300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-45300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-38900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-28200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-24400</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-27300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-25900</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-19900</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-24700</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-32400</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-37600</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-12400</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-13500</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9028,8 +9251,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9138,118 +9364,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-14700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-19100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-96000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-19100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-23300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-21300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-23200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-172200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-97500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-29500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-28100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-48200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-23300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-64200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-18300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-18100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-9800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-11600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-18800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-22700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-26500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-42600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-37100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-38000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-45300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-38900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-124200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-23100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-27300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-25900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-19100</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-43600</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-16200</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-12600</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-23300</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-11300</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9288,64 +9520,65 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>32300</v>
+      </c>
+      <c r="E96" s="3">
         <v>32200</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>32400</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>32500</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>30000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>30100</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>30200</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>30300</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>27900</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-28000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-28200</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-28300</v>
-      </c>
-      <c r="O96" s="3">
-        <v>-27200</v>
       </c>
       <c r="P96" s="3">
         <v>-27200</v>
       </c>
       <c r="Q96" s="3">
+        <v>-27200</v>
+      </c>
+      <c r="R96" s="3">
         <v>-27400</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-27700</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-26400</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-26500</v>
-      </c>
-      <c r="U96" s="3">
-        <v>-26600</v>
       </c>
       <c r="V96" s="3">
         <v>-26600</v>
@@ -9360,22 +9593,22 @@
         <v>-26600</v>
       </c>
       <c r="Z96" s="3">
+        <v>-26600</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-26800</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-24200</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-24300</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-24400</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-24500</v>
-      </c>
-      <c r="AE96" s="3">
-        <v>-23400</v>
       </c>
       <c r="AF96" s="3">
         <v>-23400</v>
@@ -9384,22 +9617,25 @@
         <v>-23400</v>
       </c>
       <c r="AH96" s="3">
+        <v>-23400</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-22900</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-23200</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-23100</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-23200</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-23300</v>
       </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9508,8 +9744,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9618,8 +9857,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9728,334 +9970,346 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-86900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-98300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>9800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-98400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-85800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-92800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-78900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-18100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-27300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-64000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-112800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-31400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-37100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-45500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-67800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-84900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-131700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-78900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-195800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>59300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-48300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-14700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-109600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-19700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-55300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>61300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-184700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-61500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-20700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-1900</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-40000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-46200</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-16300</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-55200</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-73500</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-2500</v>
+      </c>
+      <c r="E101" s="3">
         <v>3100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-5200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>9600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-9600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-4700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-5400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>9600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-9600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-4700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-5400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-2900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-1100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-2900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-600</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>7200</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>2200</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>6800</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-5800</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>1300</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-2100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-2800</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>6000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-5200</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-9000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-5000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>13300</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-1700</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>9900</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>2200</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-1600</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-2200</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-3600</v>
       </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-32100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-11500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>9000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>29900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-24000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>30700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>6600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>18400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-32300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>24600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-30400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-22000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>7500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>8000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-62700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>33400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-89900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>115400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>1100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>32200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-26000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>12600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-8700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-4800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-112600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-44900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>12600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>41200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>12500</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-400</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>34100</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>19000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-4200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DCI_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DCI_QTR_FIN.xlsx
@@ -656,518 +656,544 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="40" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45961</v>
+      </c>
+      <c r="F7" s="2">
         <v>45869</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45777</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45688</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45596</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45504</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45412</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45322</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45230</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45138</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45046</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44957</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44865</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44773</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44681</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44592</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44500</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44408</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44316</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44227</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44135</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44043</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43951</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43861</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43769</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43677</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43585</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43496</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AG7" s="2">
         <v>43404</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AH7" s="2">
         <v>43312</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AI7" s="2">
         <v>43220</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AJ7" s="2">
         <v>43131</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AK7" s="2">
         <v>43039</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AL7" s="2">
         <v>42947</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AM7" s="2">
         <v>42855</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AN7" s="2">
         <v>42766</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AO7" s="2">
         <v>42674</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AP7" s="2">
         <v>42582</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>896300</v>
+      </c>
+      <c r="E8" s="3">
+        <v>935400</v>
+      </c>
+      <c r="F8" s="3">
         <v>980700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>940100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>870000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>900100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>935400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>927900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>876700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>846300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>879500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>875700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>828300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>847300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>890000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>853200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>802500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>760900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>773100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>765000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>679100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>636600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>617400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>629700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>662000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>672700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>727000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>712800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AF8" s="3">
         <v>703700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AG8" s="3">
         <v>701400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AH8" s="3">
         <v>724700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AI8" s="3">
         <v>700000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>664700</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AK8" s="3">
         <v>644800</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AL8" s="3">
         <v>660100</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AM8" s="3">
         <v>608200</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AN8" s="3">
         <v>550600</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AO8" s="3">
         <v>553000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AP8" s="3">
         <v>593800</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>594300</v>
+      </c>
+      <c r="E9" s="3">
+        <v>604600</v>
+      </c>
+      <c r="F9" s="3">
         <v>639700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>615600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>563500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>579400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>596800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>597800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>568100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>545400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>576500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>586900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>543900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>560100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>598400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>584200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>552700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>501400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>507400</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>507000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>448000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>413900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>409500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>420500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>438800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>441400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>483200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>472100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AF9" s="3">
         <v>478300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AG9" s="3">
         <v>463000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AH9" s="3">
         <v>471700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AI9" s="3">
         <v>460400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AJ9" s="3">
         <v>445800</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AK9" s="3">
         <v>420500</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AL9" s="3">
         <v>430600</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AM9" s="3">
         <v>396700</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AN9" s="3">
         <v>362700</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AO9" s="3">
         <v>358800</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AP9" s="3">
         <v>384500</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>302000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>330800</v>
+      </c>
+      <c r="F10" s="3">
         <v>341000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>324500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>306500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>320700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>338600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>330100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>308600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>300900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>303000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>288800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>284400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>287200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>291600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>269000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>249800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>259500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>265700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>258000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>231100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>222700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>207900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>209200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>223200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>231300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>243800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>240700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AF10" s="3">
         <v>225400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AG10" s="3">
         <v>238400</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AH10" s="3">
         <v>253000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AI10" s="3">
         <v>239600</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AJ10" s="3">
         <v>218900</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AK10" s="3">
         <v>224300</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AL10" s="3">
         <v>229500</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AM10" s="3">
         <v>211500</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AN10" s="3">
         <v>187900</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AO10" s="3">
         <v>194200</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AP10" s="3">
         <v>209300</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1208,52 +1234,54 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>18600</v>
+      </c>
+      <c r="E12" s="3">
+        <v>19200</v>
+      </c>
+      <c r="F12" s="3">
         <v>22500</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>21400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>21200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>22700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>25400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>24800</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>22100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>21300</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>21900</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>19000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>18500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>18700</v>
-      </c>
-      <c r="P12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="R12" s="3" t="s">
         <v>8</v>
@@ -1324,8 +1352,14 @@
       <c r="AN12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AP12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1440,43 +1474,49 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>1800</v>
+      </c>
+      <c r="E14" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="F14" s="3">
         <v>-900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>60000</v>
       </c>
-      <c r="F14" s="3">
-        <v>6600</v>
-      </c>
-      <c r="G14" s="3">
-        <v>3300</v>
-      </c>
       <c r="H14" s="3">
+        <v>2200</v>
+      </c>
+      <c r="I14" s="3">
+        <v>1100</v>
+      </c>
+      <c r="J14" s="3">
         <v>3800</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
-        <v>21800</v>
+      <c r="L14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
+      <c r="N14" s="3">
+        <v>21800</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>8</v>
@@ -1490,23 +1530,23 @@
       <c r="R14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U14" s="3">
         <v>2500</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V14" s="3">
-        <v>14800</v>
+        <v>0</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>8</v>
+      <c r="X14" s="3">
+        <v>14800</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>8</v>
@@ -1517,11 +1557,11 @@
       <c r="AA14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="3">
-        <v>0</v>
+      <c r="AB14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD14" s="3">
         <v>0</v>
@@ -1556,55 +1596,61 @@
       <c r="AN14" s="3">
         <v>0</v>
       </c>
+      <c r="AO14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>24600</v>
+      </c>
+      <c r="E15" s="3">
+        <v>24300</v>
+      </c>
+      <c r="F15" s="3">
         <v>24400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>24600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>25000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>25500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>24900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>24600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>24600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>24300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>25000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>22500</v>
-      </c>
-      <c r="N15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O15" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="P15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
-      <c r="R15" s="3">
-        <v>0</v>
+      <c r="Q15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S15" s="3">
         <v>0</v>
@@ -1672,8 +1718,14 @@
       <c r="AN15" s="3">
         <v>0</v>
       </c>
+      <c r="AO15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1711,240 +1763,254 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>774700</v>
+      </c>
+      <c r="E17" s="3">
+        <v>792700</v>
+      </c>
+      <c r="F17" s="3">
         <v>828900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>791800</v>
       </c>
-      <c r="F17" s="3">
-        <v>736900</v>
-      </c>
-      <c r="G17" s="3">
-        <v>765100</v>
-      </c>
       <c r="H17" s="3">
+        <v>741300</v>
+      </c>
+      <c r="I17" s="3">
+        <v>767300</v>
+      </c>
+      <c r="J17" s="3">
         <v>786500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>786500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>746100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>720700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>738000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>753400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>712000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>728000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>760700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>742200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>706800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>653400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>661100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>655600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>603000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>549400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>534900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>545200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>577500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>584000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>622600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>612800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AF17" s="3">
         <v>618600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AG17" s="3">
         <v>602700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AH17" s="3">
         <v>620900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AI17" s="3">
         <v>599100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AJ17" s="3">
         <v>583100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AK17" s="3">
         <v>554100</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AL17" s="3">
         <v>565800</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AM17" s="3">
         <v>519700</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AN17" s="3">
         <v>481200</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AO17" s="3">
         <v>476600</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AP17" s="3">
         <v>503700</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>121600</v>
+      </c>
+      <c r="E18" s="3">
+        <v>142700</v>
+      </c>
+      <c r="F18" s="3">
         <v>151800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>148300</v>
       </c>
-      <c r="F18" s="3">
-        <v>133100</v>
-      </c>
-      <c r="G18" s="3">
-        <v>135000</v>
-      </c>
       <c r="H18" s="3">
+        <v>128700</v>
+      </c>
+      <c r="I18" s="3">
+        <v>132800</v>
+      </c>
+      <c r="J18" s="3">
         <v>148900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>141400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>130600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>125600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>141500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>122300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>116300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>119300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>129300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>111000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>95700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>107500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>112000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>109400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>76100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>87200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>82500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>84500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>84500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>88700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>104400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>100000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AF18" s="3">
         <v>85100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AG18" s="3">
         <v>98700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AH18" s="3">
         <v>103800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AI18" s="3">
         <v>100900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AJ18" s="3">
         <v>81600</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AK18" s="3">
         <v>90700</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AL18" s="3">
         <v>94300</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AM18" s="3">
         <v>88500</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AN18" s="3">
         <v>69400</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AO18" s="3">
         <v>76400</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AP18" s="3">
         <v>90100</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1985,588 +2051,620 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="F20" s="3">
         <v>-4100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>-4400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>-4400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>-4300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-7600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-4000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-2800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-2500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-4300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>1600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>1800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>3400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>4100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>2400</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>5100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>4700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>1100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-1500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>2700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>4300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>2800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>2600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>-400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>4700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AF20" s="3">
         <v>700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AG20" s="3">
         <v>1900</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AH20" s="3">
         <v>5300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AI20" s="3">
         <v>3500</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AJ20" s="3">
         <v>-100</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AK20" s="3">
         <v>-800</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AL20" s="3">
         <v>2500</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AM20" s="3">
         <v>600</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AN20" s="3">
         <v>1700</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AO20" s="3">
         <v>8100</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AP20" s="3">
         <v>-2700</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>150700</v>
+      </c>
+      <c r="E21" s="3">
+        <v>171600</v>
+      </c>
+      <c r="F21" s="3">
         <v>180300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>177300</v>
       </c>
-      <c r="F21" s="3">
-        <v>162500</v>
-      </c>
-      <c r="G21" s="3">
-        <v>164800</v>
-      </c>
       <c r="H21" s="3">
+        <v>158100</v>
+      </c>
+      <c r="I21" s="3">
+        <v>162600</v>
+      </c>
+      <c r="J21" s="3">
         <v>173400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>173600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>159200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>152700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>169000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>149100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>140300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>143500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>155500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>138600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>121800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>131300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>142000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>137900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>100500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>109000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>108200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>110600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>108900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>112500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>125300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>125300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AF21" s="3">
         <v>105700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AG21" s="3">
         <v>119900</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AH21" s="3">
         <v>128400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AI21" s="3">
         <v>123900</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AJ21" s="3">
         <v>100500</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AK21" s="3">
         <v>108800</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AL21" s="3">
         <v>116200</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AM21" s="3">
         <v>107600</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AN21" s="3">
         <v>89500</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AO21" s="3">
         <v>103400</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AP21" s="3">
         <v>106400</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>7700</v>
+      </c>
+      <c r="E22" s="3">
         <v>7100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
+        <v>7100</v>
+      </c>
+      <c r="G22" s="3">
         <v>5700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>5900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>5500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>5300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>5000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>5600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>5500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>4900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>5100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>4600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>4500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>4100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>3800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>3600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>3400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>3100</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>3200</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>3300</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>3500</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>3900</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>4400</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>4500</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>4700</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AD22" s="3">
         <v>5200</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AE22" s="3">
         <v>5200</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AF22" s="3">
         <v>5300</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AG22" s="3">
         <v>4200</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AH22" s="3">
         <v>5600</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AI22" s="3">
         <v>5400</v>
-      </c>
-      <c r="AH22" s="3">
-        <v>5100</v>
-      </c>
-      <c r="AI22" s="3">
-        <v>5200</v>
       </c>
       <c r="AJ22" s="3">
         <v>5100</v>
       </c>
       <c r="AK22" s="3">
-        <v>4800</v>
+        <v>5200</v>
       </c>
       <c r="AL22" s="3">
-        <v>4800</v>
+        <v>5100</v>
       </c>
       <c r="AM22" s="3">
         <v>4800</v>
       </c>
       <c r="AN22" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AO22" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AP22" s="3">
         <v>4900</v>
       </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>116600</v>
+      </c>
+      <c r="E23" s="3">
+        <v>147500</v>
+      </c>
+      <c r="F23" s="3">
         <v>149700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>87000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>125000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>130500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>139400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>144000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>129000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>122900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>117300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>121500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>113300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>116600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>128600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>111300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>94500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>104100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>114000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>110900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>73900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>82200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>81300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>84400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>82800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>86600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>98800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>99500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AF23" s="3">
         <v>80500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AG23" s="3">
         <v>96400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AH23" s="3">
         <v>103500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AI23" s="3">
         <v>99000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AJ23" s="3">
         <v>76400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AK23" s="3">
         <v>84700</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AL23" s="3">
         <v>91700</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AM23" s="3">
         <v>84300</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AN23" s="3">
         <v>66300</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AO23" s="3">
         <v>79700</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AP23" s="3">
         <v>82500</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>24100</v>
+      </c>
+      <c r="E24" s="3">
+        <v>33600</v>
+      </c>
+      <c r="F24" s="3">
         <v>35400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>29200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>29100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>31500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>29700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>30500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>30300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>30800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>25400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>27800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>27300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>29400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>27600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>28300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>22700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>27000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>29700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>26500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>17700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>20300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>17200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>21000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>18400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>21600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>21600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>24300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AF24" s="3">
         <v>20000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AG24" s="3">
         <v>23500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AH24" s="3">
         <v>27100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AI24" s="3">
         <v>28700</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AJ24" s="3">
         <v>119000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AK24" s="3">
         <v>23800</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AL24" s="3">
         <v>23500</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AM24" s="3">
         <v>24200</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AN24" s="3">
         <v>19800</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AO24" s="3">
         <v>21700</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AP24" s="3">
         <v>23000</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2681,240 +2779,258 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>92500</v>
+      </c>
+      <c r="E26" s="3">
+        <v>113900</v>
+      </c>
+      <c r="F26" s="3">
         <v>114300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>57800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>95900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>99000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>109700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>113500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>98700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>92100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>91900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>93700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>86000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>87200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>101000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>83000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>71800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>77100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>84300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>84400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>56200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>61900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>64100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>63400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>64400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>65000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>77200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>75200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AF26" s="3">
         <v>60500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AG26" s="3">
         <v>72900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AH26" s="3">
         <v>76400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AI26" s="3">
         <v>70300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AJ26" s="3">
         <v>-42600</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AK26" s="3">
         <v>60900</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AL26" s="3">
         <v>68200</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AM26" s="3">
         <v>60100</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AN26" s="3">
         <v>46500</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AO26" s="3">
         <v>58000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AP26" s="3">
         <v>59500</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>92500</v>
+      </c>
+      <c r="E27" s="3">
+        <v>113900</v>
+      </c>
+      <c r="F27" s="3">
         <v>114300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>57800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>95900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>99000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>109700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>113500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>98700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>92100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>91900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>93700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>86000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>87200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>101000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>83000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>71800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>77100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>84300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>84400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>56200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>61900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>64100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>63400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>64400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>65000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>77200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>75200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AF27" s="3">
         <v>60500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AG27" s="3">
         <v>72900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AH27" s="3">
         <v>76400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AI27" s="3">
         <v>70300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AJ27" s="3">
         <v>-42600</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AK27" s="3">
         <v>60900</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AL27" s="3">
         <v>68200</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AM27" s="3">
         <v>60100</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AN27" s="3">
         <v>46500</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AO27" s="3">
         <v>58000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AP27" s="3">
         <v>59500</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3029,8 +3145,14 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3085,11 +3207,11 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="V29" s="3" t="s">
-        <v>8</v>
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>8</v>
@@ -3106,32 +3228,32 @@
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-19100</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="3">
         <v>-400</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AG29" s="3">
         <v>900</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AH29" s="3">
         <v>26000</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AI29" s="3">
         <v>-400</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AJ29" s="3">
         <v>-10300</v>
-      </c>
-      <c r="AI29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AK29" s="3" t="s">
         <v>8</v>
@@ -3145,8 +3267,14 @@
       <c r="AN29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AP29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3261,8 +3389,14 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3377,240 +3511,258 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E32" s="3">
+        <v>4600</v>
+      </c>
+      <c r="F32" s="3">
         <v>4100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>4400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>4400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>4300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>7600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>4000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>2800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>2500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>4300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-1600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-1800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-4100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-2400</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>-5100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-4700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-1100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>1500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-2700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-4300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-2800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-2600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>-4700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AF32" s="3">
         <v>-700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AG32" s="3">
         <v>-1900</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AH32" s="3">
         <v>-5300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AI32" s="3">
         <v>-3500</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AJ32" s="3">
         <v>100</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AK32" s="3">
         <v>800</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AL32" s="3">
         <v>-2500</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AM32" s="3">
         <v>-600</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AN32" s="3">
         <v>-1700</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AO32" s="3">
         <v>-8100</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AP32" s="3">
         <v>2700</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>92500</v>
+      </c>
+      <c r="E33" s="3">
+        <v>113900</v>
+      </c>
+      <c r="F33" s="3">
         <v>114300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>57800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>95900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>99000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>109700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>113500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>98700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>92100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>91900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>93700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>86000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>87200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>101000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>83000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>71800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>77100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>84300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>84400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>56200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>61900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>64100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>63400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>64400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>65000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>58100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>75200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AF33" s="3">
         <v>60100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AG33" s="3">
         <v>73800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AH33" s="3">
         <v>102400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AI33" s="3">
         <v>69900</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AJ33" s="3">
         <v>-52900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AK33" s="3">
         <v>60900</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AL33" s="3">
         <v>68200</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AM33" s="3">
         <v>60100</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AN33" s="3">
         <v>46500</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AO33" s="3">
         <v>58000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AP33" s="3">
         <v>59500</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3725,245 +3877,263 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>92500</v>
+      </c>
+      <c r="E35" s="3">
+        <v>113900</v>
+      </c>
+      <c r="F35" s="3">
         <v>114300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>57800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>95900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>99000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>109700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>113500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>98700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>92100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>91900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>93700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>86000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>87200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>101000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>83000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>71800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>77100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>84300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>84400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>56200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>61900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>64100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>63400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>64400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>65000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>58100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>75200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AF35" s="3">
         <v>60100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AG35" s="3">
         <v>73800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AH35" s="3">
         <v>102400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AI35" s="3">
         <v>69900</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AJ35" s="3">
         <v>-52900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AK35" s="3">
         <v>60900</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AL35" s="3">
         <v>68200</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AM35" s="3">
         <v>60100</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AN35" s="3">
         <v>46500</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AO35" s="3">
         <v>58000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AP35" s="3">
         <v>59500</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45961</v>
+      </c>
+      <c r="F38" s="2">
         <v>45869</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45777</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45688</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45596</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45504</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45412</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45322</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45230</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45138</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45046</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44957</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44865</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44773</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44681</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44592</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44500</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44408</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44316</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44227</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44135</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44043</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43951</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43861</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43769</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43677</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43585</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43496</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AG38" s="2">
         <v>43404</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AH38" s="2">
         <v>43312</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AI38" s="2">
         <v>43220</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AJ38" s="2">
         <v>43131</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AK38" s="2">
         <v>43039</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AL38" s="2">
         <v>42947</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AM38" s="2">
         <v>42855</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AN38" s="2">
         <v>42766</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AO38" s="2">
         <v>42674</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AP38" s="2">
         <v>42582</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4004,8 +4174,10 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4046,124 +4218,132 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>194400</v>
+      </c>
+      <c r="E41" s="3">
+        <v>210700</v>
+      </c>
+      <c r="F41" s="3">
         <v>180400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>178500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>189100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>221200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>232700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>223700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>193800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>217800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>187100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>186000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>179400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>161000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>193300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>168700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>170400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>200800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>222800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>215300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>207300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>270000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>236600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>326500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>211100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>210000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>177800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>203800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AF41" s="3">
         <v>191200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AG41" s="3">
         <v>199900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AH41" s="3">
         <v>204700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AI41" s="3">
         <v>317300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AJ41" s="3">
         <v>362200</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AK41" s="3">
         <v>349600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AL41" s="3">
         <v>308400</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AM41" s="3">
         <v>295900</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AN41" s="3">
         <v>296300</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AO41" s="3">
         <v>262200</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AP41" s="3">
         <v>243200</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4278,540 +4458,570 @@
       <c r="AN42" s="3">
         <v>0</v>
       </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>679900</v>
+      </c>
+      <c r="E43" s="3">
+        <v>688600</v>
+      </c>
+      <c r="F43" s="3">
         <v>686500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>685800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>614200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>650100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>645600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>653200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>610500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>594400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>613000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>641700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>592200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>601100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>634300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>604200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>570900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>563400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>567600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>553800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>504300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>476900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>455300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>460500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>475800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>501500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>529500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>534300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AF43" s="3">
         <v>515300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AG43" s="3">
         <v>542400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AH43" s="3">
         <v>534600</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AI43" s="3">
         <v>530600</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AJ43" s="3">
         <v>509900</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AK43" s="3">
         <v>483000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AL43" s="3">
         <v>497700</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AM43" s="3">
         <v>459200</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AN43" s="3">
         <v>408400</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AO43" s="3">
         <v>415000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AP43" s="3">
         <v>452400</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>555800</v>
+      </c>
+      <c r="E44" s="3">
+        <v>533300</v>
+      </c>
+      <c r="F44" s="3">
         <v>513600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>529400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>540800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>520000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>476700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>444700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>433400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>429600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>418100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>449700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>501300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>490100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>502400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>510700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>480700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>444700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>384500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>360100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>347600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>329500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>322700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>346500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>350100</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>361500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>332800</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>359500</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AF44" s="3">
         <v>365600</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AG44" s="3">
         <v>360500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AH44" s="3">
         <v>334100</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AI44" s="3">
         <v>344200</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AJ44" s="3">
         <v>344900</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AK44" s="3">
         <v>319600</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AL44" s="3">
         <v>293500</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AM44" s="3">
         <v>272800</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AN44" s="3">
         <v>260400</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AO44" s="3">
         <v>249200</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AP44" s="3">
         <v>234100</v>
       </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E45" s="3">
+        <v>2900</v>
+      </c>
+      <c r="F45" s="3">
         <v>1300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>1500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>4100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>2800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>1100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>1100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>1200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>2300</v>
       </c>
-      <c r="L45" s="3" t="s">
+      <c r="N45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>1800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>76200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>83200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>76500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>83700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>92200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>86900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>69100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>69500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>67100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>67200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>82100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>87000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>84200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>86100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>82500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>76000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AF45" s="3">
         <v>85600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AG45" s="3">
         <v>67600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AH45" s="3">
         <v>52300</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AI45" s="3">
         <v>57100</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AJ45" s="3">
         <v>62900</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AK45" s="3">
         <v>52100</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AL45" s="3">
         <v>51400</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AM45" s="3">
         <v>56100</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AN45" s="3">
         <v>60100</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AO45" s="3">
         <v>66600</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AP45" s="3">
         <v>80000</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1527000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>1514400</v>
+      </c>
+      <c r="F46" s="3">
         <v>1461700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>1475500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>1422500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>1479400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>1438100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>1400700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>1317200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>1313100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>1286000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>1352600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>1349100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>1335400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>1406500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>1367300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>1314200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>1295800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>1244000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>1198700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>1126300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>1143600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>1096700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>1220500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>1121200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>1159100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>1122600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>1173600</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AF46" s="3">
         <v>1157700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AG46" s="3">
         <v>1170400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AH46" s="3">
         <v>1125700</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AI46" s="3">
         <v>1249200</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AJ46" s="3">
         <v>1279900</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AK46" s="3">
         <v>1204300</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AL46" s="3">
         <v>1151000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AM46" s="3">
         <v>1084000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AN46" s="3">
         <v>1025200</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AO46" s="3">
         <v>993000</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AP46" s="3">
         <v>1009700</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>105200</v>
+      </c>
+      <c r="E47" s="3">
+        <v>104500</v>
+      </c>
+      <c r="F47" s="3">
         <v>103600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>102000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>97700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>102700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>26900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>25900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>24300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>23500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>24400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>24300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>20500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>20400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>22400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>25600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>23700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>23900</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>24200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>24200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>23300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>22300</v>
-      </c>
-      <c r="X47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Z47" s="3" t="s">
         <v>8</v>
@@ -4819,11 +5029,11 @@
       <c r="AA47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB47" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC47" s="3">
-        <v>0</v>
+      <c r="AB47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD47" s="3">
         <v>0</v>
@@ -4858,240 +5068,258 @@
       <c r="AN47" s="3">
         <v>0</v>
       </c>
+      <c r="AO47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>645300</v>
+      </c>
+      <c r="E48" s="3">
+        <v>638900</v>
+      </c>
+      <c r="F48" s="3">
         <v>705000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>648300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>637800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>647400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>705200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>642800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>647000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>642300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>712300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>640900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>625800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>590800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>594400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>591100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>601000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>609700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>617800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>626300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>624300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>617100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>705300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>685700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>699100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>685500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>588900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>569800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AF48" s="3">
         <v>552500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AG48" s="3">
         <v>517900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AH48" s="3">
         <v>509300</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AI48" s="3">
         <v>511100</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AJ48" s="3">
         <v>507700</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AK48" s="3">
         <v>483800</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AL48" s="3">
         <v>484600</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AM48" s="3">
         <v>462500</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AN48" s="3">
         <v>459700</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AO48" s="3">
         <v>466100</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AP48" s="3">
         <v>2771000</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>599100</v>
+      </c>
+      <c r="E49" s="3">
+        <v>591200</v>
+      </c>
+      <c r="F49" s="3">
         <v>591000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>591500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>630100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>648200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>650300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>649900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>655300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>651000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>669200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>519100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>446600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>435300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>445600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>410400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>423700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>379800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>384100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>386500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>387400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>379800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>384100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>369100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>378200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>379100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>374000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>383700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AF49" s="3">
         <v>388000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AG49" s="3">
         <v>386700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AH49" s="3">
         <v>274000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AI49" s="3">
         <v>277100</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AJ49" s="3">
         <v>280200</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AK49" s="3">
         <v>277400</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AL49" s="3">
         <v>278700</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AM49" s="3">
         <v>268100</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AN49" s="3">
         <v>268800</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AO49" s="3">
         <v>270500</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AP49" s="3">
         <v>306300</v>
       </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5206,8 +5434,14 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5322,124 +5556,136 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>183800</v>
+      </c>
+      <c r="E52" s="3">
+        <v>177800</v>
+      </c>
+      <c r="F52" s="3">
         <v>115900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>179200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>173200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>165900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>93800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>146800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>139700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>138700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>78600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>138600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>136600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>130100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>131400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>124800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>128700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>129300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>130100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>118900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>109800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>106600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>58500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>63200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>63700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>59600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>57100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>78800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AF52" s="3">
         <v>68100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AG52" s="3">
         <v>69000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AH52" s="3">
         <v>67600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AI52" s="3">
         <v>57600</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AJ52" s="3">
         <v>63500</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AK52" s="3">
         <v>66900</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AL52" s="3">
         <v>65400</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AM52" s="3">
         <v>65700</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AN52" s="3">
         <v>64000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AO52" s="3">
         <v>64500</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AP52" s="3">
         <v>39700</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5554,124 +5800,136 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3060400</v>
+      </c>
+      <c r="E54" s="3">
+        <v>3026800</v>
+      </c>
+      <c r="F54" s="3">
         <v>2977200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>2996500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>2961300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>3043600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>2914300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>2866100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>2783500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>2768600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>2770500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>2675500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>2578600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>2512000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>2600300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>2519200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>2491300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>2438500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>2400200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>2354600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>2271100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>2269400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>2244600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>2338500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>2262200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>2283300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>2142600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>2205900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AF54" s="3">
         <v>2166300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AG54" s="3">
         <v>2144000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AH54" s="3">
         <v>1976600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AI54" s="3">
         <v>2095000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AJ54" s="3">
         <v>2131300</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AK54" s="3">
         <v>2032400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AL54" s="3">
         <v>1979700</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AM54" s="3">
         <v>1880300</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AN54" s="3">
         <v>1817700</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AO54" s="3">
         <v>1794100</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AP54" s="3">
         <v>1787000</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5712,8 +5970,10 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5754,704 +6014,742 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>348800</v>
+      </c>
+      <c r="E57" s="3">
+        <v>372900</v>
+      </c>
+      <c r="F57" s="3">
         <v>368600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>362000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>375200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>373500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>379400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>370000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>325800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>324900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>304900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>311100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>302100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>320700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>338500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>335800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>324500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>310000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>293900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>268100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>228100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>209400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>187700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>202700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>210100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>229100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>237500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>238700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AF57" s="3">
         <v>226700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AG57" s="3">
         <v>230600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AH57" s="3">
         <v>201300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AI57" s="3">
         <v>201500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AJ57" s="3">
         <v>200000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AK57" s="3">
         <v>190600</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AL57" s="3">
         <v>194000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AM57" s="3">
         <v>179000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AN57" s="3">
         <v>157800</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AO57" s="3">
         <v>160700</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AP57" s="3">
         <v>143300</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E58" s="3">
+        <v>9000</v>
+      </c>
+      <c r="F58" s="3">
         <v>62000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>83600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>62700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>103200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>73500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>74400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>262100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>284800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>176900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>151600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>4000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>3700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>31300</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>63900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>41200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>48500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>44500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>22400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>6700</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>9500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>58100</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>84700</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>110900</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>52300</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>50600</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AF58" s="3">
         <v>66000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AG58" s="3">
         <v>74000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AH58" s="3">
         <v>43500</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AI58" s="3">
         <v>4500</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AJ58" s="3">
         <v>18100</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AK58" s="3">
         <v>39200</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AL58" s="3">
         <v>73900</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AM58" s="3">
         <v>306900</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AN58" s="3">
         <v>277100</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AO58" s="3">
         <v>245000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AP58" s="3">
         <v>216700</v>
       </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>187700</v>
+      </c>
+      <c r="E59" s="3">
+        <v>197900</v>
+      </c>
+      <c r="F59" s="3">
         <v>180900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>179700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>215600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>188600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>187200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>167600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>195300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>162700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>153500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>143500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>274000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>248400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>287400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>239400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>250100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>230700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>264200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>236200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>249000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>203300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>209600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>172000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>203400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>191100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>193100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>157100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AF59" s="3">
         <v>200400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AG59" s="3">
         <v>183000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AH59" s="3">
         <v>224600</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AI59" s="3">
         <v>191700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AJ59" s="3">
         <v>216900</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AK59" s="3">
         <v>185300</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AL59" s="3">
         <v>216200</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AM59" s="3">
         <v>169000</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AN59" s="3">
         <v>180600</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AO59" s="3">
         <v>157700</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AP59" s="3">
         <v>183800</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>665900</v>
+      </c>
+      <c r="E60" s="3">
+        <v>703900</v>
+      </c>
+      <c r="F60" s="3">
         <v>757200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>760100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>765800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>800600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>782500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>735200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>893500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>882600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>756400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>712000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>580100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>569300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>629600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>606500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>638500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>581900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>606600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>548800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>499500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>419400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>406800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>432800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>498200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>531100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>482900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>446400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AF60" s="3">
         <v>493100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AG60" s="3">
         <v>487600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AH60" s="3">
         <v>469400</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AI60" s="3">
         <v>397700</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AJ60" s="3">
         <v>435000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AK60" s="3">
         <v>415100</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AL60" s="3">
         <v>484100</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AM60" s="3">
         <v>654900</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AN60" s="3">
         <v>615500</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AO60" s="3">
         <v>563400</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AP60" s="3">
         <v>543800</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>674300</v>
+      </c>
+      <c r="E61" s="3">
+        <v>671500</v>
+      </c>
+      <c r="F61" s="3">
         <v>668200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>638800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>514700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>538600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>524700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>481800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>352000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>366600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>539000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>470500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>624800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>600700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>644300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>607200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>553900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>548100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>461000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>454600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>495100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>576300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>617400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>735100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>595800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>596800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>584400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>644400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AF61" s="3">
         <v>632500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AG61" s="3">
         <v>630600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AH61" s="3">
         <v>499600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AI61" s="3">
         <v>687500</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AJ61" s="3">
         <v>667700</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AK61" s="3">
         <v>631700</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AL61" s="3">
         <v>537300</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AM61" s="3">
         <v>298100</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AN61" s="3">
         <v>297800</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AO61" s="3">
         <v>324700</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AP61" s="3">
         <v>350200</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>134200</v>
+      </c>
+      <c r="E62" s="3">
+        <v>124200</v>
+      </c>
+      <c r="F62" s="3">
         <v>58000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>122300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>123100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>146100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>77200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>147600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>140300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>155900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>104000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>161600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>179500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>187200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>193200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>181900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>182100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>192600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>195500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>197800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>202100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>210200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>216600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>215800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>217000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>227700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>172600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>157300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AF62" s="3">
         <v>155000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AG62" s="3">
         <v>158500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AH62" s="3">
         <v>149800</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AI62" s="3">
         <v>173400</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AJ62" s="3">
         <v>201700</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AK62" s="3">
         <v>104600</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AL62" s="3">
         <v>103800</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AM62" s="3">
         <v>125300</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AN62" s="3">
         <v>123700</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AO62" s="3">
         <v>121300</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AP62" s="3">
         <v>121600</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6566,8 +6864,14 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6682,8 +6986,14 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6798,124 +7108,136 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1485300</v>
+      </c>
+      <c r="E66" s="3">
+        <v>1510200</v>
+      </c>
+      <c r="F66" s="3">
         <v>1523700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>1532300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>1416900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>1500600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>1425200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>1382100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>1407700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>1432500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>1449800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>1376800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>1384400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>1357200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>1467100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>1395600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>1374500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>1322600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>1263100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>1201200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>1196700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>1222600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>1257500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>1399700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>1327400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>1371700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>1255300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>1266200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AF66" s="3">
         <v>1298900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AG66" s="3">
         <v>1294400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AH66" s="3">
         <v>1123600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AI66" s="3">
         <v>1263300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AJ66" s="3">
         <v>1309000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AK66" s="3">
         <v>1156100</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AL66" s="3">
         <v>1129600</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AM66" s="3">
         <v>1082600</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AN66" s="3">
         <v>1041200</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AO66" s="3">
         <v>1013500</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AP66" s="3">
         <v>1019600</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6956,8 +7278,10 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7072,8 +7396,14 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7188,8 +7518,14 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7304,8 +7640,14 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7420,124 +7762,136 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2747200</v>
+      </c>
+      <c r="E72" s="3">
+        <v>2724100</v>
+      </c>
+      <c r="F72" s="3">
         <v>2610100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>2565600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>2507800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>2476400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>2377500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>2332500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>2219000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>2180200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>2087800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>2056500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>1962800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>1932800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>1849000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>1802600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>1718000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>1700400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>1621200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>1591200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>1507600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>1504900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>1445900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>1432800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>1368600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>1361100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>1303200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>1298300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AF72" s="3">
         <v>1223800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AG72" s="3">
         <v>1213800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AH72" s="3">
         <v>1143400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AI72" s="3">
         <v>1089100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AJ72" s="3">
         <v>1016400</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AK72" s="3">
         <v>1120200</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AL72" s="3">
         <v>1056900</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AM72" s="3">
         <v>1035900</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AN72" s="3">
         <v>977300</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AO72" s="3">
         <v>977500</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AP72" s="3">
         <v>921800</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7652,8 +8006,14 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7768,8 +8128,14 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7884,124 +8250,136 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1575100</v>
+      </c>
+      <c r="E76" s="3">
+        <v>1516600</v>
+      </c>
+      <c r="F76" s="3">
         <v>1453500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>1464200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>1544400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>1543000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>1489100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>1484000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>1375800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>1336100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>1320700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>1298700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>1194200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>1154800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>1133200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>1123600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>1116800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>1115900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>1137100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>1153400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>1074400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>1046800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>987100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>938800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>934800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>911600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>887300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>939700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AF76" s="3">
         <v>867400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AG76" s="3">
         <v>849600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AH76" s="3">
         <v>853000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AI76" s="3">
         <v>831700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AJ76" s="3">
         <v>822300</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AK76" s="3">
         <v>876300</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AL76" s="3">
         <v>850100</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AM76" s="3">
         <v>797700</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AN76" s="3">
         <v>776500</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AO76" s="3">
         <v>780600</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AP76" s="3">
         <v>767400</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8116,245 +8494,263 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46053</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45961</v>
+      </c>
+      <c r="F80" s="2">
         <v>45869</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45777</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45688</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45596</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45504</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45412</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45322</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45230</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45138</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45046</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44957</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44865</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44773</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44681</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44592</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44500</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44408</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44316</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44227</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44135</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44043</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43951</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43861</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43769</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43677</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43585</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43496</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AG80" s="2">
         <v>43404</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AH80" s="2">
         <v>43312</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AI80" s="2">
         <v>43220</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AJ80" s="2">
         <v>43131</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AK80" s="2">
         <v>43039</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AL80" s="2">
         <v>42947</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AM80" s="2">
         <v>42855</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AN80" s="2">
         <v>42766</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AO80" s="2">
         <v>42674</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AP80" s="2">
         <v>42582</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>92500</v>
+      </c>
+      <c r="E81" s="3">
+        <v>113900</v>
+      </c>
+      <c r="F81" s="3">
         <v>114300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>57800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>95900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>99000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>109700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>113500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>98700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>92100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>91900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>93700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>86000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>87200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>101000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>83000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>71800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>77100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>84300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>84400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>56200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>61900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>64100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>63400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>64400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>65000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>58100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>75200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AF81" s="3">
         <v>60100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AG81" s="3">
         <v>73800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AH81" s="3">
         <v>102400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AI81" s="3">
         <v>69900</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AJ81" s="3">
         <v>-52900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AK81" s="3">
         <v>60900</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AL81" s="3">
         <v>68200</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AM81" s="3">
         <v>60100</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AN81" s="3">
         <v>46500</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AO81" s="3">
         <v>58000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AP81" s="3">
         <v>59500</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8395,124 +8791,132 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>21100</v>
+      </c>
+      <c r="E83" s="3">
+        <v>21500</v>
+      </c>
+      <c r="F83" s="3">
         <v>20900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>20700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>20800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>20300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>21600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>19600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>19800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>19900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>20500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>21100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>22400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>22400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>22800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>23500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>23700</v>
-      </c>
-      <c r="S83" s="3">
-        <v>23800</v>
-      </c>
-      <c r="T83" s="3">
-        <v>24900</v>
       </c>
       <c r="U83" s="3">
         <v>23800</v>
       </c>
       <c r="V83" s="3">
+        <v>24900</v>
+      </c>
+      <c r="W83" s="3">
+        <v>23800</v>
+      </c>
+      <c r="X83" s="3">
         <v>23300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>23300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>23000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>21800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>21600</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>21200</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>21300</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>20600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AF83" s="3">
         <v>19900</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AG83" s="3">
         <v>19300</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AH83" s="3">
         <v>19300</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AI83" s="3">
         <v>19500</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AJ83" s="3">
         <v>19000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AK83" s="3">
         <v>18900</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AL83" s="3">
         <v>19400</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AM83" s="3">
         <v>18500</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AN83" s="3">
         <v>18400</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AO83" s="3">
         <v>18900</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AP83" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8627,8 +9031,14 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8743,8 +9153,14 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8859,8 +9275,14 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8975,8 +9397,14 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9091,124 +9519,136 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>33000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>125400</v>
+      </c>
+      <c r="F89" s="3">
         <v>167800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>87700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>90400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>72900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>126000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>141500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>87000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>138000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>190800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>133200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>102300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>118200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>108900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>64100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>36900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>42900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>96300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>103300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>73400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>128900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>121800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>88400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>90700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>86100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>122600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>80400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AF89" s="3">
         <v>79500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AG89" s="3">
         <v>63300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AH89" s="3">
         <v>104200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AI89" s="3">
         <v>48900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AJ89" s="3">
         <v>45900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AK89" s="3">
         <v>63900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AL89" s="3">
         <v>87000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AM89" s="3">
         <v>61300</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AN89" s="3">
         <v>69800</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AO89" s="3">
         <v>99700</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AP89" s="3">
         <v>84200</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9249,124 +9689,132 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-14200</v>
+      </c>
+      <c r="F91" s="3">
         <v>-20300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-14700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-18900</v>
       </c>
-      <c r="G91" s="3">
-        <v>-25000</v>
-      </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
+        <v>-25100</v>
+      </c>
+      <c r="J91" s="3">
         <v>-19800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-21300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-21300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-23200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-25700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-35200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-29500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-28100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-28700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-23300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-15200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-18300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-18800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-9800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-11600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-18800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-18200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-26500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-42600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-37100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-38300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-45300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AF91" s="3">
         <v>-38900</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AG91" s="3">
         <v>-28200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AH91" s="3">
         <v>-24400</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AI91" s="3">
         <v>-27300</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AJ91" s="3">
         <v>-25900</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AK91" s="3">
         <v>-19900</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AL91" s="3">
         <v>-24700</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AM91" s="3">
         <v>-32400</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AN91" s="3">
         <v>-37600</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AO91" s="3">
         <v>-12400</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AP91" s="3">
         <v>-13500</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9481,8 +9929,14 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9597,124 +10051,136 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-3400</v>
+      </c>
+      <c r="F94" s="3">
         <v>-20600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-14700</v>
-      </c>
-      <c r="F94" s="3">
-        <v>-19100</v>
-      </c>
-      <c r="G94" s="3">
-        <v>-96000</v>
       </c>
       <c r="H94" s="3">
         <v>-19100</v>
       </c>
       <c r="I94" s="3">
+        <v>-96000</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-19100</v>
+      </c>
+      <c r="K94" s="3">
         <v>-23300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-21300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-23200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-172200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-97500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-29500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-28100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-48200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-23300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-64200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-18300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-18100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-9800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-11600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-18800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-22700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-26500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-42600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>-37100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-38000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-45300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AF94" s="3">
         <v>-38900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AG94" s="3">
         <v>-124200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AH94" s="3">
         <v>-23100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AI94" s="3">
         <v>-27300</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AJ94" s="3">
         <v>-25900</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AK94" s="3">
         <v>-19100</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AL94" s="3">
         <v>-43600</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AM94" s="3">
         <v>-16200</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AN94" s="3">
         <v>-12600</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AO94" s="3">
         <v>-23300</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AP94" s="3">
         <v>-11300</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9755,73 +10221,75 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>34600</v>
+      </c>
+      <c r="E96" s="3">
+        <v>34700</v>
+      </c>
+      <c r="F96" s="3">
         <v>35000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>32300</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>32200</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>32400</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>32500</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>30000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>30100</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>30200</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>30300</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>27900</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>-28000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>-28200</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>-28300</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>-27200</v>
       </c>
-      <c r="R96" s="3">
+      <c r="T96" s="3">
         <v>-27200</v>
       </c>
-      <c r="S96" s="3">
+      <c r="U96" s="3">
         <v>-27400</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-27700</v>
       </c>
-      <c r="U96" s="3">
+      <c r="W96" s="3">
         <v>-26400</v>
       </c>
-      <c r="V96" s="3">
+      <c r="X96" s="3">
         <v>-26500</v>
-      </c>
-      <c r="W96" s="3">
-        <v>-26600</v>
-      </c>
-      <c r="X96" s="3">
-        <v>-26600</v>
       </c>
       <c r="Y96" s="3">
         <v>-26600</v>
@@ -9833,46 +10301,52 @@
         <v>-26600</v>
       </c>
       <c r="AB96" s="3">
+        <v>-26600</v>
+      </c>
+      <c r="AC96" s="3">
+        <v>-26600</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-26800</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AE96" s="3">
         <v>-24200</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AF96" s="3">
         <v>-24300</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AG96" s="3">
         <v>-24400</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AH96" s="3">
         <v>-24500</v>
-      </c>
-      <c r="AG96" s="3">
-        <v>-23400</v>
-      </c>
-      <c r="AH96" s="3">
-        <v>-23400</v>
       </c>
       <c r="AI96" s="3">
         <v>-23400</v>
       </c>
       <c r="AJ96" s="3">
+        <v>-23400</v>
+      </c>
+      <c r="AK96" s="3">
+        <v>-23400</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-22900</v>
-      </c>
-      <c r="AK96" s="3">
-        <v>-23200</v>
-      </c>
-      <c r="AL96" s="3">
-        <v>-23100</v>
       </c>
       <c r="AM96" s="3">
         <v>-23200</v>
       </c>
       <c r="AN96" s="3">
+        <v>-23100</v>
+      </c>
+      <c r="AO96" s="3">
+        <v>-23200</v>
+      </c>
+      <c r="AP96" s="3">
         <v>-23300</v>
       </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9987,8 +10461,14 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10103,8 +10583,14 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10219,352 +10705,376 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-38400</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-93100</v>
+      </c>
+      <c r="F100" s="3">
         <v>-146300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-86900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-98300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>9800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-98400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-85800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-92800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-78900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-18100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-27300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-64000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-112800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-31400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-37100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-45500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-67800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-84900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-131700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-78900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-195800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>59300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-48300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-14700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>-109600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-19700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AF100" s="3">
         <v>-55300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AG100" s="3">
         <v>61300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AH100" s="3">
         <v>-184700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AI100" s="3">
         <v>-61500</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AJ100" s="3">
         <v>-20700</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AK100" s="3">
         <v>-1900</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AL100" s="3">
         <v>-40000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AM100" s="3">
         <v>-46200</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AN100" s="3">
         <v>-16300</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AO100" s="3">
         <v>-55200</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AP100" s="3">
         <v>-73500</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-5100</v>
+      </c>
+      <c r="E101" s="3">
+        <v>1800</v>
+      </c>
+      <c r="F101" s="3">
         <v>500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-2500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>3100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-5200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-1800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>9600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-9600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-4700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-5400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>9600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>-9600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-5400</v>
-      </c>
-      <c r="R101" s="3">
-        <v>-2900</v>
-      </c>
-      <c r="S101" s="3">
-        <v>-1100</v>
       </c>
       <c r="T101" s="3">
         <v>-2900</v>
       </c>
       <c r="U101" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="V101" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="W101" s="3">
         <v>-600</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>7200</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>2200</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>6800</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>-5800</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>1300</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>-2100</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>-2800</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AF101" s="3">
         <v>6000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AG101" s="3">
         <v>-5200</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AH101" s="3">
         <v>-9000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AI101" s="3">
         <v>-5000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AJ101" s="3">
         <v>13300</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AK101" s="3">
         <v>-1700</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AL101" s="3">
         <v>9900</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AM101" s="3">
         <v>2200</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AN101" s="3">
         <v>-1600</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AO101" s="3">
         <v>-2200</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AP101" s="3">
         <v>-3600</v>
       </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-16300</v>
+      </c>
+      <c r="E102" s="3">
+        <v>30300</v>
+      </c>
+      <c r="F102" s="3">
         <v>1900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-10600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-32100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-11500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>9000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>29900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-24000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>30700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>1100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>6600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>18400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-32300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>24600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-1700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-30400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-22000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>7500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>8000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-62700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>33400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-89900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>115400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>1100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>32200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-26000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>12600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AF102" s="3">
         <v>-8700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AG102" s="3">
         <v>-4800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AH102" s="3">
         <v>-112600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AI102" s="3">
         <v>-44900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AJ102" s="3">
         <v>12600</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AK102" s="3">
         <v>41200</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AL102" s="3">
         <v>12500</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AM102" s="3">
         <v>-400</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AN102" s="3">
         <v>34100</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AO102" s="3">
         <v>19000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AP102" s="3">
         <v>-4200</v>
       </c>
     </row>
